--- a/Excel/StockQuotation (2).xlsx
+++ b/Excel/StockQuotation (2).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>01/02/23 15:07:13</v>
+        <v>03/02/23 12:58:16</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1014.43</v>
+        <v>1011.38</v>
       </c>
       <c r="B7" t="str">
-        <v>6.68 (0.6628%)</v>
+        <v>-1.65 (-0.1628%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1015.51</v>
+        <v>1015.31</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1008.77</v>
+        <v>1008.56</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>403966142</v>
+        <v>414497627</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>12375360064.9</v>
+        <v>12032388754.08</v>
       </c>
     </row>
     <row r="9">
@@ -523,37 +523,37 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>12.8</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>12.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>83924</v>
+      </c>
+      <c r="L10">
+        <v>1082.9692</v>
+      </c>
+      <c r="M10">
+        <v>46400</v>
+      </c>
+      <c r="N10">
         <v>12.9</v>
-      </c>
-      <c r="G10">
-        <v>13.1</v>
-      </c>
-      <c r="H10">
-        <v>12.7</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>406680</v>
-      </c>
-      <c r="L10">
-        <v>5241.624</v>
-      </c>
-      <c r="M10">
-        <v>80100</v>
-      </c>
-      <c r="N10">
-        <v>12.8</v>
       </c>
       <c r="O10">
         <v>13</v>
       </c>
       <c r="P10">
-        <v>23900</v>
+        <v>64300</v>
       </c>
     </row>
     <row r="11">
@@ -564,22 +564,22 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="D11">
         <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0.49019607843137253</v>
       </c>
       <c r="F11">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="G11">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -588,22 +588,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2635801</v>
+        <v>2882659</v>
       </c>
       <c r="L11">
-        <v>52913.6477</v>
+        <v>59060.9257</v>
       </c>
       <c r="M11">
-        <v>25200</v>
+        <v>357200</v>
       </c>
       <c r="N11">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="O11">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="P11">
-        <v>904100</v>
+        <v>1158000</v>
       </c>
     </row>
     <row r="12">
@@ -614,46 +614,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E12">
-        <v>0.8620689655172413</v>
+        <v>-0.8620689655172413</v>
       </c>
       <c r="F12">
+        <v>11.6</v>
+      </c>
+      <c r="G12">
+        <v>11.6</v>
+      </c>
+      <c r="H12">
+        <v>11.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>54645283</v>
+      </c>
+      <c r="L12">
+        <v>624838.5507</v>
+      </c>
+      <c r="M12">
+        <v>10262400</v>
+      </c>
+      <c r="N12">
+        <v>11.4</v>
+      </c>
+      <c r="O12">
         <v>11.5</v>
       </c>
-      <c r="G12">
-        <v>11.7</v>
-      </c>
-      <c r="H12">
-        <v>11.5</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>48819432</v>
-      </c>
-      <c r="L12">
-        <v>565032.6522</v>
-      </c>
-      <c r="M12">
-        <v>20120000</v>
-      </c>
-      <c r="N12">
-        <v>11.6</v>
-      </c>
-      <c r="O12">
-        <v>11.7</v>
-      </c>
       <c r="P12">
-        <v>13463500</v>
+        <v>6065600</v>
       </c>
     </row>
     <row r="13">
@@ -664,46 +664,46 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="D13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.9463722397476341</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="G13">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H13">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I13">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>9827</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>4994969</v>
+        <v>2211193</v>
       </c>
       <c r="L13">
-        <v>794805.816</v>
+        <v>356945.837</v>
       </c>
       <c r="M13">
-        <v>413700</v>
+        <v>328100</v>
       </c>
       <c r="N13">
-        <v>159.5</v>
+        <v>161</v>
       </c>
       <c r="O13">
-        <v>160</v>
+        <v>161.5</v>
       </c>
       <c r="P13">
-        <v>513800</v>
+        <v>159400</v>
       </c>
     </row>
     <row r="14">
@@ -717,43 +717,43 @@
         <v>21.6</v>
       </c>
       <c r="D14">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E14">
-        <v>-0.9174311926605505</v>
+        <v>0.9345794392523364</v>
       </c>
       <c r="F14">
+        <v>21.5</v>
+      </c>
+      <c r="G14">
+        <v>21.7</v>
+      </c>
+      <c r="H14">
+        <v>21.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>6836436</v>
+      </c>
+      <c r="L14">
+        <v>147330.1925</v>
+      </c>
+      <c r="M14">
+        <v>853900</v>
+      </c>
+      <c r="N14">
+        <v>21.5</v>
+      </c>
+      <c r="O14">
         <v>21.6</v>
       </c>
-      <c r="G14">
-        <v>21.8</v>
-      </c>
-      <c r="H14">
-        <v>21.3</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>10669059</v>
-      </c>
-      <c r="L14">
-        <v>230247.2162</v>
-      </c>
-      <c r="M14">
-        <v>503300</v>
-      </c>
-      <c r="N14">
-        <v>21.6</v>
-      </c>
-      <c r="O14">
-        <v>21.7</v>
-      </c>
       <c r="P14">
-        <v>906100</v>
+        <v>289200</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>37.25</v>
+        <v>36</v>
       </c>
       <c r="D15">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="E15">
-        <v>2.0547945205479454</v>
+        <v>-2.0408163265306123</v>
       </c>
       <c r="F15">
         <v>36.75</v>
       </c>
       <c r="G15">
-        <v>37.25</v>
+        <v>37</v>
       </c>
       <c r="H15">
-        <v>36.75</v>
+        <v>36</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>2408778</v>
+        <v>4948626</v>
       </c>
       <c r="L15">
-        <v>89539.46075</v>
+        <v>178959.632</v>
       </c>
       <c r="M15">
-        <v>524000</v>
+        <v>915200</v>
       </c>
       <c r="N15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O15">
-        <v>37.25</v>
+        <v>36.25</v>
       </c>
       <c r="P15">
-        <v>446900</v>
+        <v>343900</v>
       </c>
     </row>
     <row r="16">
@@ -814,16 +814,16 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E16">
-        <v>1.015228426395939</v>
+        <v>-0.9900990099009901</v>
       </c>
       <c r="F16">
-        <v>9.95</v>
+        <v>10.1</v>
       </c>
       <c r="G16">
         <v>10.1</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>4605044</v>
+        <v>1716422</v>
       </c>
       <c r="L16">
-        <v>46055.24465</v>
+        <v>17156.9141</v>
       </c>
       <c r="M16">
-        <v>688300</v>
+        <v>679000</v>
       </c>
       <c r="N16">
         <v>9.95</v>
@@ -853,7 +853,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>587900</v>
+        <v>413600</v>
       </c>
     </row>
     <row r="17">
@@ -864,22 +864,22 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>30.25</v>
+        <v>29.75</v>
       </c>
       <c r="D17">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E17">
-        <v>1.680672268907563</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="F17">
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="G17">
-        <v>30.25</v>
+        <v>30</v>
       </c>
       <c r="H17">
-        <v>29.5</v>
+        <v>29.75</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -888,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>22075785</v>
+        <v>10127799</v>
       </c>
       <c r="L17">
-        <v>660177.36</v>
+        <v>301787.20025</v>
       </c>
       <c r="M17">
-        <v>5630400</v>
+        <v>3463300</v>
       </c>
       <c r="N17">
+        <v>29.75</v>
+      </c>
+      <c r="O17">
         <v>30</v>
       </c>
-      <c r="O17">
-        <v>30.25</v>
-      </c>
       <c r="P17">
-        <v>6205600</v>
+        <v>3613300</v>
       </c>
     </row>
     <row r="18">
@@ -914,16 +914,16 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.9900990099009901</v>
       </c>
       <c r="F18">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="G18">
         <v>10.2</v>
@@ -938,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>169832</v>
+        <v>56400</v>
       </c>
       <c r="L18">
-        <v>1716.4762</v>
+        <v>570.92</v>
       </c>
       <c r="M18">
-        <v>50100</v>
+        <v>216900</v>
       </c>
       <c r="N18">
         <v>10.1</v>
@@ -953,7 +953,7 @@
         <v>10.2</v>
       </c>
       <c r="P18">
-        <v>398600</v>
+        <v>340400</v>
       </c>
     </row>
     <row r="19">
@@ -964,22 +964,22 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>40.75</v>
+        <v>40.5</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1.2422360248447204</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>40.25</v>
+        <v>40.5</v>
       </c>
       <c r="G19">
-        <v>40.75</v>
+        <v>41</v>
       </c>
       <c r="H19">
-        <v>40.25</v>
+        <v>40.5</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -988,13 +988,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>2907598</v>
+        <v>5143625</v>
       </c>
       <c r="L19">
-        <v>117822.93</v>
+        <v>209587.5735</v>
       </c>
       <c r="M19">
-        <v>471800</v>
+        <v>477300</v>
       </c>
       <c r="N19">
         <v>40.5</v>
@@ -1003,7 +1003,7 @@
         <v>40.75</v>
       </c>
       <c r="P19">
-        <v>690500</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="20">
@@ -1014,46 +1014,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.9216589861751152</v>
+        <v>0</v>
       </c>
       <c r="F20">
+        <v>216</v>
+      </c>
+      <c r="G20">
+        <v>218</v>
+      </c>
+      <c r="H20">
+        <v>216</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>789885</v>
+      </c>
+      <c r="L20">
+        <v>171059.342</v>
+      </c>
+      <c r="M20">
+        <v>23000</v>
+      </c>
+      <c r="N20">
         <v>217</v>
       </c>
-      <c r="G20">
-        <v>220</v>
-      </c>
-      <c r="H20">
-        <v>217</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>2334973</v>
-      </c>
-      <c r="L20">
-        <v>510227.33</v>
-      </c>
-      <c r="M20">
-        <v>129600</v>
-      </c>
-      <c r="N20">
+      <c r="O20">
         <v>218</v>
       </c>
-      <c r="O20">
-        <v>219</v>
-      </c>
       <c r="P20">
-        <v>211600</v>
+        <v>84200</v>
       </c>
     </row>
     <row r="21">
@@ -1073,13 +1073,13 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G21">
         <v>38.5</v>
       </c>
       <c r="H21">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,22 +1088,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>8050562</v>
+        <v>1713313</v>
       </c>
       <c r="L21">
-        <v>305265.548</v>
+        <v>65550.448</v>
       </c>
       <c r="M21">
-        <v>203800</v>
+        <v>146800</v>
       </c>
       <c r="N21">
-        <v>38</v>
+        <v>38.25</v>
       </c>
       <c r="O21">
-        <v>38.25</v>
+        <v>38.5</v>
       </c>
       <c r="P21">
-        <v>520000</v>
+        <v>651000</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>16.8</v>
+      </c>
+      <c r="D22">
+        <v>-0.4</v>
+      </c>
+      <c r="E22">
+        <v>-2.3255813953488373</v>
+      </c>
+      <c r="F22">
+        <v>17.1</v>
+      </c>
+      <c r="G22">
         <v>17.2</v>
       </c>
-      <c r="D22">
-        <v>-0.1</v>
-      </c>
-      <c r="E22">
-        <v>-0.5780346820809249</v>
-      </c>
-      <c r="F22">
-        <v>17.3</v>
-      </c>
-      <c r="G22">
-        <v>17.4</v>
-      </c>
       <c r="H22">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>542615</v>
+        <v>2975210</v>
       </c>
       <c r="L22">
-        <v>9336.0085</v>
+        <v>50004.5643</v>
       </c>
       <c r="M22">
-        <v>265600</v>
+        <v>158600</v>
       </c>
       <c r="N22">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="O22">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="P22">
-        <v>119800</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="23">
@@ -1164,19 +1164,19 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.4854368932038835</v>
       </c>
       <c r="F23">
         <v>103.5</v>
       </c>
       <c r="G23">
-        <v>104</v>
+        <v>103.5</v>
       </c>
       <c r="H23">
         <v>102.5</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1410187</v>
+        <v>596127</v>
       </c>
       <c r="L23">
-        <v>145367.2135</v>
+        <v>61450.2335</v>
       </c>
       <c r="M23">
-        <v>187700</v>
+        <v>137100</v>
       </c>
       <c r="N23">
         <v>103</v>
@@ -1203,7 +1203,7 @@
         <v>103.5</v>
       </c>
       <c r="P23">
-        <v>240200</v>
+        <v>282300</v>
       </c>
     </row>
     <row r="24">
@@ -1217,43 +1217,43 @@
         <v>22.6</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F24">
+        <v>22.9</v>
+      </c>
+      <c r="G24">
+        <v>22.9</v>
+      </c>
+      <c r="H24">
         <v>22.6</v>
       </c>
-      <c r="G24">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>2075648</v>
+      </c>
+      <c r="L24">
+        <v>47080.1579</v>
+      </c>
+      <c r="M24">
+        <v>348500</v>
+      </c>
+      <c r="N24">
+        <v>22.6</v>
+      </c>
+      <c r="O24">
         <v>22.7</v>
       </c>
-      <c r="H24">
-        <v>22.4</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>2576242</v>
-      </c>
-      <c r="L24">
-        <v>58054.296</v>
-      </c>
-      <c r="M24">
-        <v>209500</v>
-      </c>
-      <c r="N24">
-        <v>22.5</v>
-      </c>
-      <c r="O24">
-        <v>22.6</v>
-      </c>
       <c r="P24">
-        <v>369500</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="25">
@@ -1264,13 +1264,13 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="D25">
         <v>0.04</v>
       </c>
       <c r="E25">
-        <v>0.8849557522123894</v>
+        <v>0.8810572687224669</v>
       </c>
       <c r="F25">
         <v>4.54</v>
@@ -1279,7 +1279,7 @@
         <v>4.58</v>
       </c>
       <c r="H25">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>14796744</v>
+        <v>1178350</v>
       </c>
       <c r="L25">
-        <v>67300.43088</v>
+        <v>5383.643</v>
       </c>
       <c r="M25">
-        <v>641200</v>
+        <v>857200</v>
       </c>
       <c r="N25">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="O25">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="P25">
-        <v>556600</v>
+        <v>1046500</v>
       </c>
     </row>
     <row r="26">
@@ -1314,22 +1314,22 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D26">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1.271186440677966</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G26">
         <v>24</v>
       </c>
       <c r="H26">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,22 +1338,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>16205955</v>
+        <v>9578760</v>
       </c>
       <c r="L26">
-        <v>386709.6731</v>
+        <v>228593.6587</v>
       </c>
       <c r="M26">
-        <v>2576300</v>
+        <v>1523800</v>
       </c>
       <c r="N26">
+        <v>23.8</v>
+      </c>
+      <c r="O26">
         <v>23.9</v>
       </c>
-      <c r="O26">
-        <v>24</v>
-      </c>
       <c r="P26">
-        <v>3653500</v>
+        <v>474400</v>
       </c>
     </row>
     <row r="27">
@@ -1364,22 +1364,22 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>43.25</v>
+        <v>44.5</v>
       </c>
       <c r="D27">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="E27">
-        <v>1.7647058823529411</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="F27">
-        <v>42.75</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>43.5</v>
+        <v>44.75</v>
       </c>
       <c r="H27">
-        <v>42.75</v>
+        <v>43.75</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>4018712</v>
+        <v>5789252</v>
       </c>
       <c r="L27">
-        <v>173807.8355</v>
+        <v>255629.49225</v>
       </c>
       <c r="M27">
-        <v>1065800</v>
+        <v>1007200</v>
       </c>
       <c r="N27">
-        <v>43.25</v>
+        <v>44.5</v>
       </c>
       <c r="O27">
-        <v>43.5</v>
+        <v>44.75</v>
       </c>
       <c r="P27">
-        <v>1474000</v>
+        <v>888400</v>
       </c>
     </row>
     <row r="28">
@@ -1414,19 +1414,19 @@
         <v>-</v>
       </c>
       <c r="C28">
+        <v>8.35</v>
+      </c>
+      <c r="D28">
+        <v>0.05</v>
+      </c>
+      <c r="E28">
+        <v>0.6024096385542169</v>
+      </c>
+      <c r="F28">
         <v>8.3</v>
       </c>
-      <c r="D28">
-        <v>-0.1</v>
-      </c>
-      <c r="E28">
-        <v>-1.1904761904761905</v>
-      </c>
-      <c r="F28">
-        <v>8.4</v>
-      </c>
       <c r="G28">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="H28">
         <v>8.3</v>
@@ -1438,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>246866</v>
+        <v>5287</v>
       </c>
       <c r="L28">
-        <v>2067.7608</v>
+        <v>44.0471</v>
       </c>
       <c r="M28">
-        <v>58300</v>
+        <v>15500</v>
       </c>
       <c r="N28">
         <v>8.3</v>
       </c>
       <c r="O28">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="P28">
-        <v>96100</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="29">
@@ -1467,16 +1467,16 @@
         <v>173.5</v>
       </c>
       <c r="D29">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E29">
-        <v>-0.28735632183908044</v>
+        <v>-0.5730659025787965</v>
       </c>
       <c r="F29">
         <v>174</v>
       </c>
       <c r="G29">
-        <v>175.5</v>
+        <v>175</v>
       </c>
       <c r="H29">
         <v>173.5</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>365279</v>
+        <v>254316</v>
       </c>
       <c r="L29">
-        <v>63597.92</v>
+        <v>44194.1755</v>
       </c>
       <c r="M29">
-        <v>105500</v>
+        <v>52200</v>
       </c>
       <c r="N29">
         <v>173.5</v>
@@ -1503,7 +1503,7 @@
         <v>174</v>
       </c>
       <c r="P29">
-        <v>82600</v>
+        <v>58700</v>
       </c>
     </row>
     <row r="30">
@@ -1514,46 +1514,46 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D30">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E30">
-        <v>0.9615384615384616</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="F30">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="G30">
+        <v>21.2</v>
+      </c>
+      <c r="H30">
+        <v>20.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>7827538</v>
+      </c>
+      <c r="L30">
+        <v>164164.5855</v>
+      </c>
+      <c r="M30">
+        <v>366800</v>
+      </c>
+      <c r="N30">
         <v>21.1</v>
       </c>
-      <c r="H30">
-        <v>20.8</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>4134376</v>
-      </c>
-      <c r="L30">
-        <v>86662.6627</v>
-      </c>
-      <c r="M30">
-        <v>824500</v>
-      </c>
-      <c r="N30">
-        <v>20.9</v>
-      </c>
       <c r="O30">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="P30">
-        <v>468800</v>
+        <v>1111100</v>
       </c>
     </row>
     <row r="31">
@@ -1567,19 +1567,19 @@
         <v>69.5</v>
       </c>
       <c r="D31">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="E31">
-        <v>1.0909090909090908</v>
+        <v>0.36101083032490977</v>
       </c>
       <c r="F31">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="G31">
-        <v>69.75</v>
+        <v>70</v>
       </c>
       <c r="H31">
-        <v>68.75</v>
+        <v>69.25</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>2879140</v>
+        <v>3217833</v>
       </c>
       <c r="L31">
-        <v>200308.57375</v>
+        <v>224379.00775</v>
       </c>
       <c r="M31">
-        <v>298000</v>
+        <v>255900</v>
       </c>
       <c r="N31">
         <v>69.5</v>
@@ -1603,7 +1603,7 @@
         <v>69.75</v>
       </c>
       <c r="P31">
-        <v>478900</v>
+        <v>171900</v>
       </c>
     </row>
     <row r="32">
@@ -1614,46 +1614,46 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>54.25</v>
+        <v>54</v>
       </c>
       <c r="D32">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E32">
-        <v>0.9302325581395349</v>
+        <v>0.46511627906976744</v>
       </c>
       <c r="F32">
+        <v>53.75</v>
+      </c>
+      <c r="G32">
         <v>54</v>
       </c>
-      <c r="G32">
-        <v>54.5</v>
-      </c>
       <c r="H32">
+        <v>53.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>4045359</v>
+      </c>
+      <c r="L32">
+        <v>217544.964</v>
+      </c>
+      <c r="M32">
+        <v>474400</v>
+      </c>
+      <c r="N32">
         <v>53.75</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>7632834</v>
-      </c>
-      <c r="L32">
-        <v>412768.39725</v>
-      </c>
-      <c r="M32">
-        <v>3246600</v>
-      </c>
-      <c r="N32">
+      <c r="O32">
         <v>54</v>
       </c>
-      <c r="O32">
-        <v>54.25</v>
-      </c>
       <c r="P32">
-        <v>1062300</v>
+        <v>887700</v>
       </c>
     </row>
     <row r="33">
@@ -1664,19 +1664,19 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="D33">
-        <v>0.07</v>
+        <v>-0.02</v>
       </c>
       <c r="E33">
-        <v>1.4056224899598393</v>
+        <v>-0.4</v>
       </c>
       <c r="F33">
         <v>5</v>
       </c>
       <c r="G33">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>4.98</v>
@@ -1688,22 +1688,22 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>32114911</v>
+        <v>3485277</v>
       </c>
       <c r="L33">
-        <v>160715.02985</v>
+        <v>17380.11324</v>
       </c>
       <c r="M33">
-        <v>8258600</v>
+        <v>4818900</v>
       </c>
       <c r="N33">
+        <v>4.98</v>
+      </c>
+      <c r="O33">
         <v>5</v>
       </c>
-      <c r="O33">
-        <v>5.05</v>
-      </c>
       <c r="P33">
-        <v>14373300</v>
+        <v>3493200</v>
       </c>
     </row>
     <row r="34">
@@ -1714,46 +1714,46 @@
         <v>-</v>
       </c>
       <c r="C34">
+        <v>12.5</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>12.4</v>
       </c>
-      <c r="D34">
-        <v>0.3</v>
-      </c>
-      <c r="E34">
-        <v>2.479338842975207</v>
-      </c>
-      <c r="F34">
-        <v>12.1</v>
-      </c>
       <c r="G34">
+        <v>12.5</v>
+      </c>
+      <c r="H34">
+        <v>12.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2221074</v>
+      </c>
+      <c r="L34">
+        <v>27533.5165</v>
+      </c>
+      <c r="M34">
+        <v>140300</v>
+      </c>
+      <c r="N34">
         <v>12.4</v>
       </c>
-      <c r="H34">
-        <v>11.8</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>7647032</v>
-      </c>
-      <c r="L34">
-        <v>92731.34479999999</v>
-      </c>
-      <c r="M34">
-        <v>814600</v>
-      </c>
-      <c r="N34">
-        <v>12.3</v>
-      </c>
       <c r="O34">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="P34">
-        <v>2157800</v>
+        <v>413200</v>
       </c>
     </row>
     <row r="35">
@@ -1767,19 +1767,19 @@
         <v>73.5</v>
       </c>
       <c r="D35">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E35">
-        <v>1.0309278350515463</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="F35">
-        <v>72.5</v>
+        <v>72.75</v>
       </c>
       <c r="G35">
-        <v>73.75</v>
+        <v>74</v>
       </c>
       <c r="H35">
-        <v>72.5</v>
+        <v>72.75</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,13 +1788,13 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>1003004</v>
+        <v>802203</v>
       </c>
       <c r="L35">
-        <v>73480.325</v>
+        <v>58812.5405</v>
       </c>
       <c r="M35">
-        <v>118700</v>
+        <v>85100</v>
       </c>
       <c r="N35">
         <v>73.25</v>
@@ -1803,7 +1803,7 @@
         <v>73.5</v>
       </c>
       <c r="P35">
-        <v>44600</v>
+        <v>37400</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="D36">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E36">
-        <v>1.3071895424836601</v>
+        <v>-1.3071895424836601</v>
       </c>
       <c r="F36">
         <v>3.08</v>
       </c>
       <c r="G36">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="H36">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>31140095</v>
+        <v>45863127</v>
       </c>
       <c r="L36">
-        <v>96370.41116</v>
+        <v>139544.70306</v>
       </c>
       <c r="M36">
-        <v>4555000</v>
+        <v>14972900</v>
       </c>
       <c r="N36">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P36">
-        <v>2787100</v>
+        <v>6129300</v>
       </c>
     </row>
     <row r="37">
@@ -1864,19 +1864,19 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>21.3</v>
+      </c>
+      <c r="D37">
+        <v>0.1</v>
+      </c>
+      <c r="E37">
+        <v>0.4716981132075472</v>
+      </c>
+      <c r="F37">
+        <v>21.2</v>
+      </c>
+      <c r="G37">
         <v>21.4</v>
-      </c>
-      <c r="D37">
-        <v>-0.1</v>
-      </c>
-      <c r="E37">
-        <v>-0.46511627906976744</v>
-      </c>
-      <c r="F37">
-        <v>21.5</v>
-      </c>
-      <c r="G37">
-        <v>21.6</v>
       </c>
       <c r="H37">
         <v>21.2</v>
@@ -1888,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>2099125</v>
+        <v>1299710</v>
       </c>
       <c r="L37">
-        <v>44867.4274</v>
+        <v>27678.966</v>
       </c>
       <c r="M37">
-        <v>152000</v>
+        <v>134500</v>
       </c>
       <c r="N37">
         <v>21.3</v>
@@ -1903,7 +1903,7 @@
         <v>21.4</v>
       </c>
       <c r="P37">
-        <v>152000</v>
+        <v>109800</v>
       </c>
     </row>
     <row r="38">
@@ -1914,46 +1914,46 @@
         <v>-</v>
       </c>
       <c r="C38">
+        <v>144</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>144.5</v>
+      </c>
+      <c r="G38">
         <v>145</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>145</v>
-      </c>
-      <c r="G38">
-        <v>146</v>
-      </c>
       <c r="H38">
+        <v>143.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>5620646</v>
+      </c>
+      <c r="L38">
+        <v>810120.921</v>
+      </c>
+      <c r="M38">
+        <v>1805600</v>
+      </c>
+      <c r="N38">
+        <v>143.5</v>
+      </c>
+      <c r="O38">
         <v>144</v>
       </c>
-      <c r="I38">
-        <v>170000</v>
-      </c>
-      <c r="J38">
-        <v>24565</v>
-      </c>
-      <c r="K38">
-        <v>11979669</v>
-      </c>
-      <c r="L38">
-        <v>1733528.86</v>
-      </c>
-      <c r="M38">
-        <v>811800</v>
-      </c>
-      <c r="N38">
-        <v>144.5</v>
-      </c>
-      <c r="O38">
-        <v>145</v>
-      </c>
       <c r="P38">
-        <v>718300</v>
+        <v>305800</v>
       </c>
     </row>
     <row r="39">
@@ -1964,46 +1964,46 @@
         <v>-</v>
       </c>
       <c r="C39">
+        <v>68</v>
+      </c>
+      <c r="D39">
+        <v>-0.5</v>
+      </c>
+      <c r="E39">
+        <v>-0.7299270072992701</v>
+      </c>
+      <c r="F39">
         <v>68.75</v>
       </c>
-      <c r="D39">
-        <v>0.5</v>
-      </c>
-      <c r="E39">
-        <v>0.7326007326007326</v>
-      </c>
-      <c r="F39">
-        <v>68.5</v>
-      </c>
       <c r="G39">
-        <v>69</v>
+        <v>68.75</v>
       </c>
       <c r="H39">
+        <v>68</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>3221568</v>
+      </c>
+      <c r="L39">
+        <v>220126.521</v>
+      </c>
+      <c r="M39">
+        <v>1284000</v>
+      </c>
+      <c r="N39">
+        <v>68</v>
+      </c>
+      <c r="O39">
         <v>68.25</v>
       </c>
-      <c r="I39">
-        <v>100000</v>
-      </c>
-      <c r="J39">
-        <v>6825</v>
-      </c>
-      <c r="K39">
-        <v>3870002</v>
-      </c>
-      <c r="L39">
-        <v>265243.08525</v>
-      </c>
-      <c r="M39">
-        <v>241200</v>
-      </c>
-      <c r="N39">
-        <v>68.75</v>
-      </c>
-      <c r="O39">
-        <v>69</v>
-      </c>
       <c r="P39">
-        <v>534200</v>
+        <v>311600</v>
       </c>
     </row>
     <row r="40">
@@ -2014,16 +2014,16 @@
         <v>-</v>
       </c>
       <c r="C40">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="D40">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E40">
-        <v>2.2099447513812156</v>
+        <v>-0.5434782608695652</v>
       </c>
       <c r="F40">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G40">
         <v>3.72</v>
@@ -2038,22 +2038,22 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>12986497</v>
+        <v>2406000</v>
       </c>
       <c r="L40">
-        <v>48007.01798</v>
+        <v>8891.812</v>
       </c>
       <c r="M40">
-        <v>1000800</v>
+        <v>475500</v>
       </c>
       <c r="N40">
+        <v>3.66</v>
+      </c>
+      <c r="O40">
         <v>3.68</v>
       </c>
-      <c r="O40">
-        <v>3.7</v>
-      </c>
       <c r="P40">
-        <v>861500</v>
+        <v>175600</v>
       </c>
     </row>
     <row r="41">
@@ -2064,46 +2064,46 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="D41">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>2.127659574468085</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="G41">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="H41">
+        <v>18.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>756276</v>
+      </c>
+      <c r="L41">
+        <v>14094.438300000002</v>
+      </c>
+      <c r="M41">
+        <v>93000</v>
+      </c>
+      <c r="N41">
         <v>18.7</v>
       </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>3205143</v>
-      </c>
-      <c r="L41">
-        <v>60564.413700000005</v>
-      </c>
-      <c r="M41">
-        <v>153400</v>
-      </c>
-      <c r="N41">
-        <v>19.1</v>
-      </c>
       <c r="O41">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="P41">
-        <v>379600</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="42">
@@ -2117,19 +2117,19 @@
         <v>51.5</v>
       </c>
       <c r="D42">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E42">
-        <v>-1.4354066985645932</v>
+        <v>-0.9615384615384616</v>
       </c>
       <c r="F42">
         <v>52</v>
       </c>
       <c r="G42">
-        <v>52.25</v>
+        <v>52</v>
       </c>
       <c r="H42">
-        <v>51</v>
+        <v>51.25</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2138,22 +2138,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>822478</v>
+        <v>837619</v>
       </c>
       <c r="L42">
-        <v>42288.667</v>
+        <v>43140.9105</v>
       </c>
       <c r="M42">
-        <v>111900</v>
+        <v>221800</v>
       </c>
       <c r="N42">
+        <v>51.25</v>
+      </c>
+      <c r="O42">
         <v>51.5</v>
       </c>
-      <c r="O42">
-        <v>51.75</v>
-      </c>
       <c r="P42">
-        <v>76300</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="43">
@@ -2164,23 +2164,23 @@
         <v>-</v>
       </c>
       <c r="C43">
+        <v>33.75</v>
+      </c>
+      <c r="D43">
+        <v>0.25</v>
+      </c>
+      <c r="E43">
+        <v>0.746268656716418</v>
+      </c>
+      <c r="F43">
+        <v>33.75</v>
+      </c>
+      <c r="G43">
+        <v>34</v>
+      </c>
+      <c r="H43">
         <v>33.25</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>33.5</v>
-      </c>
-      <c r="G43">
-        <v>33.5</v>
-      </c>
-      <c r="H43">
-        <v>32.75</v>
-      </c>
       <c r="I43">
         <v>0</v>
       </c>
@@ -2188,22 +2188,22 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>8184025</v>
+        <v>7461410</v>
       </c>
       <c r="L43">
-        <v>270701.79175</v>
+        <v>252144.407</v>
       </c>
       <c r="M43">
-        <v>2228600</v>
+        <v>1659400</v>
       </c>
       <c r="N43">
-        <v>33</v>
+        <v>33.75</v>
       </c>
       <c r="O43">
-        <v>33.25</v>
+        <v>34</v>
       </c>
       <c r="P43">
-        <v>3613500</v>
+        <v>1891500</v>
       </c>
     </row>
     <row r="44">
@@ -2214,46 +2214,46 @@
         <v>-</v>
       </c>
       <c r="C44">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="D44">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E44">
-        <v>-0.44642857142857145</v>
+        <v>0.44642857142857145</v>
       </c>
       <c r="F44">
         <v>22.4</v>
       </c>
       <c r="G44">
+        <v>22.7</v>
+      </c>
+      <c r="H44">
+        <v>22.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>5808000</v>
+      </c>
+      <c r="L44">
+        <v>131181.3141</v>
+      </c>
+      <c r="M44">
+        <v>1419600</v>
+      </c>
+      <c r="N44">
         <v>22.5</v>
       </c>
-      <c r="H44">
-        <v>22.3</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>9896287</v>
-      </c>
-      <c r="L44">
-        <v>221588.4042</v>
-      </c>
-      <c r="M44">
-        <v>5947500</v>
-      </c>
-      <c r="N44">
-        <v>22.3</v>
-      </c>
       <c r="O44">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="P44">
-        <v>2485000</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="45">
@@ -2267,19 +2267,19 @@
         <v>28.25</v>
       </c>
       <c r="D45">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E45">
-        <v>0.8928571428571429</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F45">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="G45">
         <v>28.5</v>
       </c>
       <c r="H45">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>1722724</v>
+        <v>1108746</v>
       </c>
       <c r="L45">
-        <v>48646.9095</v>
+        <v>31330.526</v>
       </c>
       <c r="M45">
-        <v>510900</v>
+        <v>639800</v>
       </c>
       <c r="N45">
         <v>28.25</v>
@@ -2303,7 +2303,7 @@
         <v>28.5</v>
       </c>
       <c r="P45">
-        <v>2873400</v>
+        <v>1398300</v>
       </c>
     </row>
     <row r="46">
@@ -2314,7 +2314,7 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2323,37 +2323,37 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="G46">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="H46">
+        <v>32.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>37092275</v>
+      </c>
+      <c r="L46">
+        <v>1217492.49675</v>
+      </c>
+      <c r="M46">
+        <v>13678200</v>
+      </c>
+      <c r="N46">
+        <v>32.75</v>
+      </c>
+      <c r="O46">
         <v>33</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>21001307</v>
-      </c>
-      <c r="L46">
-        <v>697562.74825</v>
-      </c>
-      <c r="M46">
-        <v>16988000</v>
-      </c>
-      <c r="N46">
-        <v>33</v>
-      </c>
-      <c r="O46">
-        <v>33.25</v>
-      </c>
       <c r="P46">
-        <v>9901100</v>
+        <v>10779800</v>
       </c>
     </row>
     <row r="47">
@@ -2364,22 +2364,22 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D47">
-        <v>1.5</v>
+        <v>-4</v>
       </c>
       <c r="E47">
-        <v>0.8746355685131195</v>
+        <v>-2.3529411764705883</v>
       </c>
       <c r="F47">
-        <v>172</v>
+        <v>169.5</v>
       </c>
       <c r="G47">
-        <v>173.5</v>
+        <v>169.5</v>
       </c>
       <c r="H47">
-        <v>172</v>
+        <v>164.5</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2388,22 +2388,22 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>3977158</v>
+        <v>20392736</v>
       </c>
       <c r="L47">
-        <v>687409.0705</v>
+        <v>3387949.05</v>
       </c>
       <c r="M47">
-        <v>547700</v>
+        <v>773000</v>
       </c>
       <c r="N47">
-        <v>172.5</v>
+        <v>166</v>
       </c>
       <c r="O47">
-        <v>173</v>
+        <v>166.5</v>
       </c>
       <c r="P47">
-        <v>400900</v>
+        <v>252600</v>
       </c>
     </row>
     <row r="48">
@@ -2414,16 +2414,16 @@
         <v>-</v>
       </c>
       <c r="C48">
-        <v>49.75</v>
+        <v>49.5</v>
       </c>
       <c r="D48">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E48">
-        <v>1.015228426395939</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F48">
-        <v>49.25</v>
+        <v>50</v>
       </c>
       <c r="G48">
         <v>50</v>
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>8076826</v>
+        <v>3436893</v>
       </c>
       <c r="L48">
-        <v>402540.71475</v>
+        <v>170335.43975</v>
       </c>
       <c r="M48">
-        <v>850000</v>
+        <v>618200</v>
       </c>
       <c r="N48">
+        <v>49.5</v>
+      </c>
+      <c r="O48">
         <v>49.75</v>
       </c>
-      <c r="O48">
-        <v>50</v>
-      </c>
       <c r="P48">
-        <v>849700</v>
+        <v>275200</v>
       </c>
     </row>
     <row r="49">
@@ -2464,46 +2464,46 @@
         <v>-</v>
       </c>
       <c r="C49">
+        <v>43.25</v>
+      </c>
+      <c r="D49">
+        <v>0.25</v>
+      </c>
+      <c r="E49">
+        <v>0.5813953488372093</v>
+      </c>
+      <c r="F49">
+        <v>42.75</v>
+      </c>
+      <c r="G49">
+        <v>43.25</v>
+      </c>
+      <c r="H49">
+        <v>42.75</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>1069275</v>
+      </c>
+      <c r="L49">
+        <v>45962.1565</v>
+      </c>
+      <c r="M49">
+        <v>169400</v>
+      </c>
+      <c r="N49">
         <v>43</v>
       </c>
-      <c r="D49">
-        <v>0.75</v>
-      </c>
-      <c r="E49">
-        <v>1.7751479289940828</v>
-      </c>
-      <c r="F49">
-        <v>42.25</v>
-      </c>
-      <c r="G49">
-        <v>43</v>
-      </c>
-      <c r="H49">
-        <v>42.25</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>3416178</v>
-      </c>
-      <c r="L49">
-        <v>145370.98725</v>
-      </c>
-      <c r="M49">
-        <v>512500</v>
-      </c>
-      <c r="N49">
-        <v>42.75</v>
-      </c>
       <c r="O49">
-        <v>43</v>
+        <v>43.25</v>
       </c>
       <c r="P49">
-        <v>541100</v>
+        <v>433700</v>
       </c>
     </row>
     <row r="50">
@@ -2514,46 +2514,46 @@
         <v>-</v>
       </c>
       <c r="C50">
+        <v>13</v>
+      </c>
+      <c r="D50">
+        <v>0.1</v>
+      </c>
+      <c r="E50">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="F50">
+        <v>13</v>
+      </c>
+      <c r="G50">
+        <v>13.1</v>
+      </c>
+      <c r="H50">
         <v>12.9</v>
       </c>
-      <c r="D50">
-        <v>0.2</v>
-      </c>
-      <c r="E50">
-        <v>1.5748031496062993</v>
-      </c>
-      <c r="F50">
-        <v>12.7</v>
-      </c>
-      <c r="G50">
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>688022</v>
+      </c>
+      <c r="L50">
+        <v>8931.6222</v>
+      </c>
+      <c r="M50">
+        <v>214500</v>
+      </c>
+      <c r="N50">
         <v>12.9</v>
       </c>
-      <c r="H50">
-        <v>12.5</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>2072105</v>
-      </c>
-      <c r="L50">
-        <v>26263.3941</v>
-      </c>
-      <c r="M50">
-        <v>285500</v>
-      </c>
-      <c r="N50">
-        <v>12.8</v>
-      </c>
       <c r="O50">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="P50">
-        <v>436400</v>
+        <v>327700</v>
       </c>
     </row>
     <row r="51">
@@ -2564,19 +2564,19 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>30.75</v>
+        <v>31</v>
       </c>
       <c r="D51">
-        <v>-2</v>
+        <v>0.75</v>
       </c>
       <c r="E51">
-        <v>-6.106870229007634</v>
+        <v>2.479338842975207</v>
       </c>
       <c r="F51">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="G51">
-        <v>32.25</v>
+        <v>31</v>
       </c>
       <c r="H51">
         <v>30.5</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>13052674</v>
+        <v>1326990</v>
       </c>
       <c r="L51">
-        <v>403702.38925</v>
+        <v>40796.9215</v>
       </c>
       <c r="M51">
-        <v>1235800</v>
+        <v>209300</v>
       </c>
       <c r="N51">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="O51">
-        <v>30.75</v>
+        <v>31</v>
       </c>
       <c r="P51">
-        <v>200400</v>
+        <v>536800</v>
       </c>
     </row>
     <row r="52">
@@ -2614,22 +2614,22 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="D52">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E52">
-        <v>-2.6785714285714284</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F52">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G52">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="H52">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>2852400</v>
+        <v>16569929</v>
       </c>
       <c r="L52">
-        <v>15564.565</v>
+        <v>96573.90879999999</v>
       </c>
       <c r="M52">
-        <v>951400</v>
+        <v>692300</v>
       </c>
       <c r="N52">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="O52">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="P52">
-        <v>38200</v>
+        <v>145200</v>
       </c>
     </row>
     <row r="53">
@@ -2664,37 +2664,37 @@
         <v>-</v>
       </c>
       <c r="C53">
+        <v>104.5</v>
+      </c>
+      <c r="D53">
+        <v>-0.5</v>
+      </c>
+      <c r="E53">
+        <v>-0.47619047619047616</v>
+      </c>
+      <c r="F53">
         <v>105</v>
       </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="F53">
+      <c r="G53">
+        <v>105.5</v>
+      </c>
+      <c r="H53">
         <v>104.5</v>
       </c>
-      <c r="G53">
-        <v>105</v>
-      </c>
-      <c r="H53">
-        <v>104</v>
-      </c>
       <c r="I53">
-        <v>155000</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>16120</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>3531682</v>
+        <v>684901</v>
       </c>
       <c r="L53">
-        <v>370357.132</v>
+        <v>71852.403</v>
       </c>
       <c r="M53">
-        <v>1430200</v>
+        <v>1115600</v>
       </c>
       <c r="N53">
         <v>104.5</v>
@@ -2703,7 +2703,7 @@
         <v>105</v>
       </c>
       <c r="P53">
-        <v>1642700</v>
+        <v>1364400</v>
       </c>
     </row>
     <row r="54">
@@ -2717,43 +2717,43 @@
         <v>339</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54">
-        <v>0.8928571428571429</v>
+        <v>0.2958579881656805</v>
       </c>
       <c r="F54">
         <v>337</v>
       </c>
       <c r="G54">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H54">
         <v>337</v>
       </c>
       <c r="I54">
-        <v>383600</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>128889.6</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>1036541</v>
+        <v>1875224</v>
       </c>
       <c r="L54">
-        <v>350434.217</v>
+        <v>634175.786</v>
       </c>
       <c r="M54">
-        <v>80400</v>
+        <v>111400</v>
       </c>
       <c r="N54">
+        <v>338</v>
+      </c>
+      <c r="O54">
         <v>339</v>
       </c>
-      <c r="O54">
-        <v>340</v>
-      </c>
       <c r="P54">
-        <v>346900</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="55">
@@ -2764,46 +2764,46 @@
         <v>-</v>
       </c>
       <c r="C55">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D55">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E55">
-        <v>0.31347962382445144</v>
+        <v>-0.31347962382445144</v>
       </c>
       <c r="F55">
-        <v>159.5</v>
+        <v>160.5</v>
       </c>
       <c r="G55">
         <v>160.5</v>
       </c>
       <c r="H55">
+        <v>158</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>173063</v>
+      </c>
+      <c r="L55">
+        <v>27487.9135</v>
+      </c>
+      <c r="M55">
+        <v>500</v>
+      </c>
+      <c r="N55">
+        <v>159</v>
+      </c>
+      <c r="O55">
         <v>159.5</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>33591</v>
-      </c>
-      <c r="L55">
-        <v>5375.02</v>
-      </c>
-      <c r="M55">
-        <v>10800</v>
-      </c>
-      <c r="N55">
-        <v>160</v>
-      </c>
-      <c r="O55">
-        <v>160.5</v>
-      </c>
       <c r="P55">
-        <v>30600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="56">
@@ -2817,34 +2817,34 @@
         <v>53.5</v>
       </c>
       <c r="D56">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="E56">
-        <v>2.3923444976076556</v>
+        <v>0.4694835680751174</v>
       </c>
       <c r="F56">
-        <v>52.75</v>
+        <v>53.5</v>
       </c>
       <c r="G56">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
       <c r="H56">
-        <v>52.5</v>
+        <v>53.25</v>
       </c>
       <c r="I56">
-        <v>58294</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>3045.8615</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>5112585</v>
+        <v>1702870</v>
       </c>
       <c r="L56">
-        <v>271231.35575</v>
+        <v>91093.57375</v>
       </c>
       <c r="M56">
-        <v>779900</v>
+        <v>739000</v>
       </c>
       <c r="N56">
         <v>53.25</v>
@@ -2853,7 +2853,7 @@
         <v>53.5</v>
       </c>
       <c r="P56">
-        <v>872500</v>
+        <v>609700</v>
       </c>
     </row>
     <row r="57">
@@ -2864,22 +2864,22 @@
         <v>-</v>
       </c>
       <c r="C57">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="D57">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E57">
-        <v>0.8695652173913043</v>
+        <v>-2.6315789473684212</v>
       </c>
       <c r="F57">
+        <v>11.4</v>
+      </c>
+      <c r="G57">
         <v>11.5</v>
       </c>
-      <c r="G57">
-        <v>11.6</v>
-      </c>
       <c r="H57">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2888,22 +2888,22 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>19278746</v>
+        <v>16051623</v>
       </c>
       <c r="L57">
-        <v>222067.2254</v>
+        <v>179251.83419999998</v>
       </c>
       <c r="M57">
-        <v>3204800</v>
+        <v>1518500</v>
       </c>
       <c r="N57">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="O57">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="P57">
-        <v>954900</v>
+        <v>374700</v>
       </c>
     </row>
     <row r="58">
@@ -2914,7 +2914,7 @@
         <v>-</v>
       </c>
       <c r="C58">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G58">
         <v>10.1</v>
@@ -2938,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>1341409</v>
+        <v>441648</v>
       </c>
       <c r="L58">
-        <v>13472.601</v>
+        <v>4417.4496</v>
       </c>
       <c r="M58">
-        <v>726400</v>
+        <v>45100</v>
       </c>
       <c r="N58">
         <v>10</v>
@@ -2953,7 +2953,7 @@
         <v>10.1</v>
       </c>
       <c r="P58">
-        <v>612000</v>
+        <v>324500</v>
       </c>
     </row>
     <row r="59">
@@ -2964,22 +2964,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="D59">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E59">
-        <v>1.9230769230769231</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F59">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="G59">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="H59">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>2986286</v>
+        <v>13236816</v>
       </c>
       <c r="L59">
-        <v>31201.9269</v>
+        <v>150250.6619</v>
       </c>
       <c r="M59">
-        <v>740000</v>
+        <v>847700</v>
       </c>
       <c r="N59">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="O59">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="P59">
-        <v>647700</v>
+        <v>280100</v>
       </c>
     </row>
     <row r="60">
@@ -3014,19 +3014,19 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="D60">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>1.5873015873015872</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G60">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H60">
         <v>0.63</v>
@@ -3038,22 +3038,22 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>3721509</v>
+        <v>68803870</v>
       </c>
       <c r="L60">
-        <v>2373.79566</v>
+        <v>44046.87118</v>
       </c>
       <c r="M60">
-        <v>35869300</v>
+        <v>2583200</v>
       </c>
       <c r="N60">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="O60">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="P60">
-        <v>10527700</v>
+        <v>38593700</v>
       </c>
     </row>
     <row r="61">
@@ -3064,46 +3064,46 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="D61">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E61">
-        <v>-0.5494505494505495</v>
+        <v>1.694915254237288</v>
       </c>
       <c r="F61">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="G61">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="H61">
+        <v>17.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>4474887</v>
+      </c>
+      <c r="L61">
+        <v>80421.125</v>
+      </c>
+      <c r="M61">
+        <v>846800</v>
+      </c>
+      <c r="N61">
+        <v>17.9</v>
+      </c>
+      <c r="O61">
         <v>18</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>5353761</v>
-      </c>
-      <c r="L61">
-        <v>97014.5085</v>
-      </c>
-      <c r="M61">
-        <v>357900</v>
-      </c>
-      <c r="N61">
-        <v>18</v>
-      </c>
-      <c r="O61">
-        <v>18.1</v>
-      </c>
       <c r="P61">
-        <v>249700</v>
+        <v>323200</v>
       </c>
     </row>
     <row r="62">
@@ -3114,46 +3114,46 @@
         <v>-</v>
       </c>
       <c r="C62">
+        <v>16.2</v>
+      </c>
+      <c r="D62">
+        <v>0.1</v>
+      </c>
+      <c r="E62">
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="F62">
+        <v>16.2</v>
+      </c>
+      <c r="G62">
         <v>16.3</v>
       </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>16.3</v>
-      </c>
-      <c r="G62">
-        <v>16.4</v>
-      </c>
       <c r="H62">
+        <v>16</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>2458468</v>
+      </c>
+      <c r="L62">
+        <v>39842.401600000005</v>
+      </c>
+      <c r="M62">
+        <v>339400</v>
+      </c>
+      <c r="N62">
+        <v>16.1</v>
+      </c>
+      <c r="O62">
         <v>16.2</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>1881628</v>
-      </c>
-      <c r="L62">
-        <v>30594.457300000002</v>
-      </c>
-      <c r="M62">
-        <v>184800</v>
-      </c>
-      <c r="N62">
-        <v>16.2</v>
-      </c>
-      <c r="O62">
-        <v>16.3</v>
-      </c>
       <c r="P62">
-        <v>144400</v>
+        <v>115300</v>
       </c>
     </row>
     <row r="63">
@@ -3164,22 +3164,22 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>58.75</v>
+        <v>57.25</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="E63">
-        <v>1.7316017316017316</v>
+        <v>-0.8658008658008658</v>
       </c>
       <c r="F63">
+        <v>57.75</v>
+      </c>
+      <c r="G63">
         <v>58</v>
       </c>
-      <c r="G63">
-        <v>59</v>
-      </c>
       <c r="H63">
-        <v>58</v>
+        <v>56.75</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3188,22 +3188,22 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>6102394</v>
+        <v>7565247</v>
       </c>
       <c r="L63">
-        <v>357734.15425</v>
+        <v>432750.8315</v>
       </c>
       <c r="M63">
-        <v>338200</v>
+        <v>467600</v>
       </c>
       <c r="N63">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="O63">
-        <v>58.75</v>
+        <v>57.25</v>
       </c>
       <c r="P63">
-        <v>421300</v>
+        <v>722600</v>
       </c>
     </row>
     <row r="64">
@@ -3214,22 +3214,22 @@
         <v>-</v>
       </c>
       <c r="C64">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>-0.8264462809917356</v>
       </c>
       <c r="F64">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="G64">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="H64">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3238,22 +3238,22 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>1405201</v>
+        <v>1779100</v>
       </c>
       <c r="L64">
-        <v>1635.14517</v>
+        <v>2153.838</v>
       </c>
       <c r="M64">
-        <v>307400</v>
+        <v>779800</v>
       </c>
       <c r="N64">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="O64">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P64">
-        <v>373800</v>
+        <v>339700</v>
       </c>
     </row>
     <row r="65">
@@ -3264,22 +3264,22 @@
         <v>-</v>
       </c>
       <c r="C65">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D65">
         <v>0.1</v>
       </c>
       <c r="E65">
-        <v>0.625</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F65">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="G65">
         <v>16.2</v>
       </c>
       <c r="H65">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>5752506</v>
+        <v>4613789</v>
       </c>
       <c r="L65">
-        <v>92521.8391</v>
+        <v>74294.3007</v>
       </c>
       <c r="M65">
-        <v>2000400</v>
+        <v>1120400</v>
       </c>
       <c r="N65">
         <v>16.1</v>
@@ -3303,7 +3303,7 @@
         <v>16.2</v>
       </c>
       <c r="P65">
-        <v>2370800</v>
+        <v>2225000</v>
       </c>
     </row>
     <row r="66">
@@ -3314,46 +3314,46 @@
         <v>-</v>
       </c>
       <c r="C66">
+        <v>5.55</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>5.5</v>
+      </c>
+      <c r="G66">
         <v>5.6</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>5.6</v>
-      </c>
-      <c r="G66">
-        <v>5.65</v>
-      </c>
       <c r="H66">
+        <v>5.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>356500</v>
+      </c>
+      <c r="L66">
+        <v>1968.645</v>
+      </c>
+      <c r="M66">
+        <v>226000</v>
+      </c>
+      <c r="N66">
+        <v>5.5</v>
+      </c>
+      <c r="O66">
         <v>5.55</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>265200</v>
-      </c>
-      <c r="L66">
-        <v>1478.385</v>
-      </c>
-      <c r="M66">
-        <v>20800</v>
-      </c>
-      <c r="N66">
-        <v>5.55</v>
-      </c>
-      <c r="O66">
-        <v>5.6</v>
-      </c>
       <c r="P66">
-        <v>31900</v>
+        <v>38200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (2).xlsx
+++ b/Excel/StockQuotation (2).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:16</v>
+        <v>07/02/23 23:29:43</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1011.38</v>
+        <v>1008.43</v>
       </c>
       <c r="B7" t="str">
-        <v>-1.65 (-0.1628%)</v>
+        <v>0.39 (0.0386%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1015.31</v>
+        <v>1010.7</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1008.56</v>
+        <v>1002.49</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>414497627</v>
+        <v>699120426</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>12032388754.08</v>
+        <v>19003898633.81</v>
       </c>
     </row>
     <row r="9">
@@ -517,16 +517,16 @@
         <v>12.9</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>-0.7692307692307693</v>
       </c>
       <c r="F10">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H10">
         <v>12.8</v>
@@ -538,22 +538,22 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>83924</v>
+        <v>296417</v>
       </c>
       <c r="L10">
-        <v>1082.9692</v>
+        <v>3835.5916</v>
       </c>
       <c r="M10">
-        <v>46400</v>
+        <v>86000</v>
       </c>
       <c r="N10">
+        <v>12.8</v>
+      </c>
+      <c r="O10">
         <v>12.9</v>
       </c>
-      <c r="O10">
-        <v>13</v>
-      </c>
       <c r="P10">
-        <v>64300</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="11">
@@ -564,22 +564,22 @@
         <v>-</v>
       </c>
       <c r="C11">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.49019607843137253</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="G11">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="H11">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -588,22 +588,22 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2882659</v>
+        <v>6175226</v>
       </c>
       <c r="L11">
-        <v>59060.9257</v>
+        <v>124102.2675</v>
       </c>
       <c r="M11">
-        <v>357200</v>
+        <v>171800</v>
       </c>
       <c r="N11">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="O11">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="P11">
-        <v>1158000</v>
+        <v>143600</v>
       </c>
     </row>
     <row r="12">
@@ -614,46 +614,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="D12">
         <v>-0.1</v>
       </c>
       <c r="E12">
-        <v>-0.8620689655172413</v>
+        <v>-0.8849557522123894</v>
       </c>
       <c r="F12">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G12">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H12">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="K12">
-        <v>54645283</v>
+        <v>161516144</v>
       </c>
       <c r="L12">
-        <v>624838.5507</v>
+        <v>1831534.3802</v>
       </c>
       <c r="M12">
-        <v>10262400</v>
+        <v>23883600</v>
       </c>
       <c r="N12">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="O12">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="P12">
-        <v>6065600</v>
+        <v>772100</v>
       </c>
     </row>
     <row r="13">
@@ -664,22 +664,22 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>-0.3105590062111801</v>
       </c>
       <c r="F13">
         <v>161.5</v>
       </c>
       <c r="G13">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="H13">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>2211193</v>
+        <v>3101777</v>
       </c>
       <c r="L13">
-        <v>356945.837</v>
+        <v>497468.5115</v>
       </c>
       <c r="M13">
-        <v>328100</v>
+        <v>756800</v>
       </c>
       <c r="N13">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O13">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="P13">
-        <v>159400</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="14">
@@ -714,22 +714,22 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="D14">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E14">
-        <v>0.9345794392523364</v>
+        <v>-0.9389671361502347</v>
       </c>
       <c r="F14">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="G14">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="H14">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>6836436</v>
+        <v>11021734</v>
       </c>
       <c r="L14">
-        <v>147330.1925</v>
+        <v>232419.2244</v>
       </c>
       <c r="M14">
-        <v>853900</v>
+        <v>2048300</v>
       </c>
       <c r="N14">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="O14">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="P14">
-        <v>289200</v>
+        <v>189800</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
+        <v>35.5</v>
+      </c>
+      <c r="D15">
+        <v>-0.5</v>
+      </c>
+      <c r="E15">
+        <v>-1.3888888888888888</v>
+      </c>
+      <c r="F15">
         <v>36</v>
       </c>
-      <c r="D15">
-        <v>-0.75</v>
-      </c>
-      <c r="E15">
-        <v>-2.0408163265306123</v>
-      </c>
-      <c r="F15">
-        <v>36.75</v>
-      </c>
       <c r="G15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>36</v>
+        <v>35.25</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>4948626</v>
+        <v>5801589</v>
       </c>
       <c r="L15">
-        <v>178959.632</v>
+        <v>206626.30275</v>
       </c>
       <c r="M15">
-        <v>915200</v>
+        <v>767100</v>
       </c>
       <c r="N15">
-        <v>36</v>
+        <v>35.25</v>
       </c>
       <c r="O15">
-        <v>36.25</v>
+        <v>35.5</v>
       </c>
       <c r="P15">
-        <v>343900</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="16">
@@ -817,10 +817,10 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>10.1</v>
@@ -829,7 +829,7 @@
         <v>10.1</v>
       </c>
       <c r="H16">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -838,22 +838,22 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1716422</v>
+        <v>1404493</v>
       </c>
       <c r="L16">
-        <v>17156.9141</v>
+        <v>14074.1795</v>
       </c>
       <c r="M16">
-        <v>679000</v>
+        <v>640200</v>
       </c>
       <c r="N16">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="P16">
-        <v>413600</v>
+        <v>895700</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="D17">
         <v>-0.25</v>
       </c>
       <c r="E17">
-        <v>-0.8333333333333334</v>
+        <v>-0.8403361344537815</v>
       </c>
       <c r="F17">
-        <v>29.75</v>
+        <v>30</v>
       </c>
       <c r="G17">
         <v>30</v>
       </c>
       <c r="H17">
+        <v>29.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>21781654</v>
+      </c>
+      <c r="L17">
+        <v>646621.64125</v>
+      </c>
+      <c r="M17">
+        <v>9700400</v>
+      </c>
+      <c r="N17">
+        <v>29.5</v>
+      </c>
+      <c r="O17">
         <v>29.75</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>10127799</v>
-      </c>
-      <c r="L17">
-        <v>301787.20025</v>
-      </c>
-      <c r="M17">
-        <v>3463300</v>
-      </c>
-      <c r="N17">
-        <v>29.75</v>
-      </c>
-      <c r="O17">
-        <v>30</v>
-      </c>
       <c r="P17">
-        <v>3613300</v>
+        <v>1863000</v>
       </c>
     </row>
     <row r="18">
@@ -914,23 +914,23 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D18">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>10.2</v>
       </c>
       <c r="G18">
+        <v>10.4</v>
+      </c>
+      <c r="H18">
         <v>10.2</v>
       </c>
-      <c r="H18">
-        <v>10.1</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>56400</v>
+        <v>321738</v>
       </c>
       <c r="L18">
-        <v>570.92</v>
+        <v>3312.4498</v>
       </c>
       <c r="M18">
-        <v>216900</v>
+        <v>918600</v>
       </c>
       <c r="N18">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="O18">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="P18">
-        <v>340400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="19">
@@ -964,22 +964,22 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>40.5</v>
+        <v>40.75</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>2.5157232704402515</v>
       </c>
       <c r="F19">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="G19">
-        <v>41</v>
+        <v>40.75</v>
       </c>
       <c r="H19">
-        <v>40.5</v>
+        <v>39.75</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -988,13 +988,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5143625</v>
+        <v>9101197</v>
       </c>
       <c r="L19">
-        <v>209587.5735</v>
+        <v>365517.13</v>
       </c>
       <c r="M19">
-        <v>477300</v>
+        <v>464700</v>
       </c>
       <c r="N19">
         <v>40.5</v>
@@ -1003,7 +1003,7 @@
         <v>40.75</v>
       </c>
       <c r="P19">
-        <v>390000</v>
+        <v>724300</v>
       </c>
     </row>
     <row r="20">
@@ -1014,46 +1014,46 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>-0.46511627906976744</v>
       </c>
       <c r="F20">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G20">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H20">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2910.4</v>
       </c>
       <c r="K20">
-        <v>789885</v>
+        <v>2593682</v>
       </c>
       <c r="L20">
-        <v>171059.342</v>
+        <v>553752.373</v>
       </c>
       <c r="M20">
-        <v>23000</v>
+        <v>315500</v>
       </c>
       <c r="N20">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O20">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P20">
-        <v>84200</v>
+        <v>204300</v>
       </c>
     </row>
     <row r="21">
@@ -1064,46 +1064,46 @@
         <v>-</v>
       </c>
       <c r="C21">
+        <v>38.5</v>
+      </c>
+      <c r="D21">
+        <v>0.5</v>
+      </c>
+      <c r="E21">
+        <v>1.3157894736842106</v>
+      </c>
+      <c r="F21">
         <v>38.25</v>
       </c>
-      <c r="D21">
-        <v>0.25</v>
-      </c>
-      <c r="E21">
-        <v>0.6578947368421053</v>
-      </c>
-      <c r="F21">
+      <c r="G21">
+        <v>38.75</v>
+      </c>
+      <c r="H21">
+        <v>37.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>4774943</v>
+      </c>
+      <c r="L21">
+        <v>182526.64975</v>
+      </c>
+      <c r="M21">
+        <v>374200</v>
+      </c>
+      <c r="N21">
         <v>38.5</v>
       </c>
-      <c r="G21">
-        <v>38.5</v>
-      </c>
-      <c r="H21">
-        <v>38</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1713313</v>
-      </c>
-      <c r="L21">
-        <v>65550.448</v>
-      </c>
-      <c r="M21">
-        <v>146800</v>
-      </c>
-      <c r="N21">
-        <v>38.25</v>
-      </c>
       <c r="O21">
-        <v>38.5</v>
+        <v>38.75</v>
       </c>
       <c r="P21">
-        <v>651000</v>
+        <v>403100</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="D22">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E22">
-        <v>-2.3255813953488373</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F22">
         <v>17.1</v>
       </c>
       <c r="G22">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="H22">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>2975210</v>
+        <v>551835</v>
       </c>
       <c r="L22">
-        <v>50004.5643</v>
+        <v>9361.9499</v>
       </c>
       <c r="M22">
-        <v>158600</v>
+        <v>17000</v>
       </c>
       <c r="N22">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="O22">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="P22">
-        <v>73900</v>
+        <v>228900</v>
       </c>
     </row>
     <row r="23">
@@ -1164,22 +1164,22 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="D23">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E23">
-        <v>0.4854368932038835</v>
+        <v>-0.970873786407767</v>
       </c>
       <c r="F23">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="G23">
         <v>103.5</v>
       </c>
       <c r="H23">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1188,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>596127</v>
+        <v>1768116</v>
       </c>
       <c r="L23">
-        <v>61450.2335</v>
+        <v>180572.946</v>
       </c>
       <c r="M23">
-        <v>137100</v>
+        <v>151600</v>
       </c>
       <c r="N23">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="O23">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="P23">
-        <v>282300</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="24">
@@ -1214,46 +1214,46 @@
         <v>-</v>
       </c>
       <c r="C24">
+        <v>22.4</v>
+      </c>
+      <c r="D24">
+        <v>-0.3</v>
+      </c>
+      <c r="E24">
+        <v>-1.3215859030837005</v>
+      </c>
+      <c r="F24">
         <v>22.6</v>
       </c>
-      <c r="D24">
-        <v>-0.2</v>
-      </c>
-      <c r="E24">
-        <v>-0.8771929824561403</v>
-      </c>
-      <c r="F24">
-        <v>22.9</v>
-      </c>
       <c r="G24">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="H24">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="K24">
-        <v>2075648</v>
+        <v>5067398</v>
       </c>
       <c r="L24">
-        <v>47080.1579</v>
+        <v>114296.93509999999</v>
       </c>
       <c r="M24">
-        <v>348500</v>
+        <v>600600</v>
       </c>
       <c r="N24">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="O24">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="P24">
-        <v>263600</v>
+        <v>71100</v>
       </c>
     </row>
     <row r="25">
@@ -1264,22 +1264,22 @@
         <v>-</v>
       </c>
       <c r="C25">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="D25">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E25">
-        <v>0.8810572687224669</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="F25">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="G25">
-        <v>4.58</v>
+        <v>4.72</v>
       </c>
       <c r="H25">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>1178350</v>
+        <v>24336619</v>
       </c>
       <c r="L25">
-        <v>5383.643</v>
+        <v>113698.60182</v>
       </c>
       <c r="M25">
-        <v>857200</v>
+        <v>1189900</v>
       </c>
       <c r="N25">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
       <c r="O25">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="P25">
-        <v>1046500</v>
+        <v>359000</v>
       </c>
     </row>
     <row r="26">
@@ -1314,7 +1314,7 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G26">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="H26">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,22 +1338,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>9578760</v>
+        <v>17028962</v>
       </c>
       <c r="L26">
-        <v>228593.6587</v>
+        <v>401183.07739999995</v>
       </c>
       <c r="M26">
-        <v>1523800</v>
+        <v>2056100</v>
       </c>
       <c r="N26">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="O26">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="P26">
-        <v>474400</v>
+        <v>347500</v>
       </c>
     </row>
     <row r="27">
@@ -1364,19 +1364,19 @@
         <v>-</v>
       </c>
       <c r="C27">
+        <v>44.25</v>
+      </c>
+      <c r="D27">
+        <v>-0.25</v>
+      </c>
+      <c r="E27">
+        <v>-0.5617977528089888</v>
+      </c>
+      <c r="F27">
         <v>44.5</v>
       </c>
-      <c r="D27">
-        <v>0.25</v>
-      </c>
-      <c r="E27">
-        <v>0.5649717514124294</v>
-      </c>
-      <c r="F27">
-        <v>44</v>
-      </c>
       <c r="G27">
-        <v>44.75</v>
+        <v>44.5</v>
       </c>
       <c r="H27">
         <v>43.75</v>
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>5789252</v>
+        <v>10167453</v>
       </c>
       <c r="L27">
-        <v>255629.49225</v>
+        <v>448185.82275</v>
       </c>
       <c r="M27">
-        <v>1007200</v>
+        <v>667100</v>
       </c>
       <c r="N27">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="O27">
-        <v>44.75</v>
+        <v>44.25</v>
       </c>
       <c r="P27">
-        <v>888400</v>
+        <v>1198400</v>
       </c>
     </row>
     <row r="28">
@@ -1414,46 +1414,46 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="D28">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E28">
-        <v>0.6024096385542169</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F28">
+        <v>8.25</v>
+      </c>
+      <c r="G28">
         <v>8.3</v>
       </c>
-      <c r="G28">
-        <v>8.35</v>
-      </c>
       <c r="H28">
+        <v>8.25</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>137355</v>
+      </c>
+      <c r="L28">
+        <v>1134.4045</v>
+      </c>
+      <c r="M28">
+        <v>11800</v>
+      </c>
+      <c r="N28">
+        <v>8.25</v>
+      </c>
+      <c r="O28">
         <v>8.3</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>5287</v>
-      </c>
-      <c r="L28">
-        <v>44.0471</v>
-      </c>
-      <c r="M28">
-        <v>15500</v>
-      </c>
-      <c r="N28">
-        <v>8.3</v>
-      </c>
-      <c r="O28">
-        <v>8.35</v>
-      </c>
       <c r="P28">
-        <v>46600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="29">
@@ -1464,22 +1464,22 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="E29">
-        <v>-0.5730659025787965</v>
+        <v>-0.2898550724637681</v>
       </c>
       <c r="F29">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G29">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H29">
-        <v>173.5</v>
+        <v>171</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>254316</v>
+        <v>944769</v>
       </c>
       <c r="L29">
-        <v>44194.1755</v>
+        <v>162568.3245</v>
       </c>
       <c r="M29">
-        <v>52200</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="O29">
-        <v>174</v>
+        <v>172.5</v>
       </c>
       <c r="P29">
-        <v>58700</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="30">
@@ -1514,19 +1514,19 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D30">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="G30">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="H30">
         <v>20.7</v>
@@ -1538,22 +1538,22 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>7827538</v>
+        <v>11074770</v>
       </c>
       <c r="L30">
-        <v>164164.5855</v>
+        <v>230826.29940000002</v>
       </c>
       <c r="M30">
-        <v>366800</v>
+        <v>9800</v>
       </c>
       <c r="N30">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="O30">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="P30">
-        <v>1111100</v>
+        <v>851900</v>
       </c>
     </row>
     <row r="31">
@@ -1567,43 +1567,43 @@
         <v>69.5</v>
       </c>
       <c r="D31">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E31">
-        <v>0.36101083032490977</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="F31">
+        <v>69</v>
+      </c>
+      <c r="G31">
+        <v>69.75</v>
+      </c>
+      <c r="H31">
+        <v>69</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>3829162</v>
+      </c>
+      <c r="L31">
+        <v>265731.12725</v>
+      </c>
+      <c r="M31">
+        <v>160600</v>
+      </c>
+      <c r="N31">
+        <v>69.25</v>
+      </c>
+      <c r="O31">
         <v>69.5</v>
       </c>
-      <c r="G31">
-        <v>70</v>
-      </c>
-      <c r="H31">
-        <v>69.25</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>3217833</v>
-      </c>
-      <c r="L31">
-        <v>224379.00775</v>
-      </c>
-      <c r="M31">
-        <v>255900</v>
-      </c>
-      <c r="N31">
-        <v>69.5</v>
-      </c>
-      <c r="O31">
-        <v>69.75</v>
-      </c>
       <c r="P31">
-        <v>171900</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="32">
@@ -1626,10 +1626,10 @@
         <v>53.75</v>
       </c>
       <c r="G32">
-        <v>54</v>
+        <v>54.25</v>
       </c>
       <c r="H32">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1638,13 +1638,13 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>4045359</v>
+        <v>11502957</v>
       </c>
       <c r="L32">
-        <v>217544.964</v>
+        <v>620947.3135</v>
       </c>
       <c r="M32">
-        <v>474400</v>
+        <v>3345400</v>
       </c>
       <c r="N32">
         <v>53.75</v>
@@ -1653,7 +1653,7 @@
         <v>54</v>
       </c>
       <c r="P32">
-        <v>887700</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="33">
@@ -1664,46 +1664,46 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="D33">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E33">
-        <v>-0.4</v>
+        <v>-0.8032128514056225</v>
       </c>
       <c r="F33">
         <v>5</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H33">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2865.2</v>
       </c>
       <c r="K33">
-        <v>3485277</v>
+        <v>52248036</v>
       </c>
       <c r="L33">
-        <v>17380.11324</v>
+        <v>259856.6892</v>
       </c>
       <c r="M33">
-        <v>4818900</v>
+        <v>7270900</v>
       </c>
       <c r="N33">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="P33">
-        <v>3493200</v>
+        <v>43100</v>
       </c>
     </row>
     <row r="34">
@@ -1714,23 +1714,23 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F34">
+        <v>12.6</v>
+      </c>
+      <c r="G34">
+        <v>12.7</v>
+      </c>
+      <c r="H34">
         <v>12.4</v>
       </c>
-      <c r="G34">
-        <v>12.5</v>
-      </c>
-      <c r="H34">
-        <v>12.3</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
@@ -1738,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>2221074</v>
+        <v>3613668</v>
       </c>
       <c r="L34">
-        <v>27533.5165</v>
+        <v>45327.817299999995</v>
       </c>
       <c r="M34">
-        <v>140300</v>
+        <v>656600</v>
       </c>
       <c r="N34">
         <v>12.4</v>
@@ -1753,7 +1753,7 @@
         <v>12.5</v>
       </c>
       <c r="P34">
-        <v>413200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="35">
@@ -1764,46 +1764,46 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="D35">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E35">
-        <v>0.684931506849315</v>
+        <v>-0.3436426116838488</v>
       </c>
       <c r="F35">
         <v>72.75</v>
       </c>
       <c r="G35">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H35">
+        <v>72.25</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1572591</v>
+      </c>
+      <c r="L35">
+        <v>114134.26675</v>
+      </c>
+      <c r="M35">
+        <v>25400</v>
+      </c>
+      <c r="N35">
+        <v>72.5</v>
+      </c>
+      <c r="O35">
         <v>72.75</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>802203</v>
-      </c>
-      <c r="L35">
-        <v>58812.5405</v>
-      </c>
-      <c r="M35">
-        <v>85100</v>
-      </c>
-      <c r="N35">
-        <v>73.25</v>
-      </c>
-      <c r="O35">
-        <v>73.5</v>
-      </c>
       <c r="P35">
-        <v>37400</v>
+        <v>154600</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="D36">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E36">
-        <v>-1.3071895424836601</v>
+        <v>-0.6535947712418301</v>
       </c>
       <c r="F36">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="G36">
         <v>3.08</v>
       </c>
       <c r="H36">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>45863127</v>
+        <v>19508263</v>
       </c>
       <c r="L36">
-        <v>139544.70306</v>
+        <v>59583.11662</v>
       </c>
       <c r="M36">
-        <v>14972900</v>
+        <v>10848100</v>
       </c>
       <c r="N36">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="O36">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="P36">
-        <v>6129300</v>
+        <v>1410300</v>
       </c>
     </row>
     <row r="37">
@@ -1864,22 +1864,22 @@
         <v>-</v>
       </c>
       <c r="C37">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="D37">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E37">
-        <v>0.4716981132075472</v>
+        <v>-0.9569377990430622</v>
       </c>
       <c r="F37">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="G37">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="H37">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1299710</v>
+        <v>5033514</v>
       </c>
       <c r="L37">
-        <v>27678.966</v>
+        <v>104421.0835</v>
       </c>
       <c r="M37">
-        <v>134500</v>
+        <v>167300</v>
       </c>
       <c r="N37">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="O37">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="P37">
-        <v>109800</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="38">
@@ -1914,37 +1914,37 @@
         <v>-</v>
       </c>
       <c r="C38">
+        <v>143.5</v>
+      </c>
+      <c r="D38">
+        <v>-0.5</v>
+      </c>
+      <c r="E38">
+        <v>-0.3472222222222222</v>
+      </c>
+      <c r="F38">
         <v>144</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
+      <c r="G38">
         <v>144.5</v>
-      </c>
-      <c r="G38">
-        <v>145</v>
       </c>
       <c r="H38">
         <v>143.5</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="K38">
-        <v>5620646</v>
+        <v>7124224</v>
       </c>
       <c r="L38">
-        <v>810120.921</v>
+        <v>1025018.0965</v>
       </c>
       <c r="M38">
-        <v>1805600</v>
+        <v>1601200</v>
       </c>
       <c r="N38">
         <v>143.5</v>
@@ -1953,7 +1953,7 @@
         <v>144</v>
       </c>
       <c r="P38">
-        <v>305800</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="39">
@@ -1964,46 +1964,46 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="D39">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E39">
-        <v>-0.7299270072992701</v>
+        <v>-1.4598540145985401</v>
       </c>
       <c r="F39">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="G39">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="H39">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="K39">
-        <v>3221568</v>
+        <v>9986259</v>
       </c>
       <c r="L39">
-        <v>220126.521</v>
+        <v>675593.27775</v>
       </c>
       <c r="M39">
-        <v>1284000</v>
+        <v>688400</v>
       </c>
       <c r="N39">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="O39">
-        <v>68.25</v>
+        <v>67.5</v>
       </c>
       <c r="P39">
-        <v>311600</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="40">
@@ -2017,19 +2017,19 @@
         <v>3.66</v>
       </c>
       <c r="D40">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>-0.5434782608695652</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="G40">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="H40">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>2406000</v>
+        <v>4525592</v>
       </c>
       <c r="L40">
-        <v>8891.812</v>
+        <v>16602.01504</v>
       </c>
       <c r="M40">
-        <v>475500</v>
+        <v>711200</v>
       </c>
       <c r="N40">
         <v>3.66</v>
@@ -2053,7 +2053,7 @@
         <v>3.68</v>
       </c>
       <c r="P40">
-        <v>175600</v>
+        <v>86300</v>
       </c>
     </row>
     <row r="41">
@@ -2064,13 +2064,13 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>-1.0638297872340425</v>
       </c>
       <c r="F41">
         <v>18.7</v>
@@ -2079,7 +2079,7 @@
         <v>18.8</v>
       </c>
       <c r="H41">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>756276</v>
+        <v>1235687</v>
       </c>
       <c r="L41">
-        <v>14094.438300000002</v>
+        <v>23003.4544</v>
       </c>
       <c r="M41">
-        <v>93000</v>
+        <v>122700</v>
       </c>
       <c r="N41">
+        <v>18.6</v>
+      </c>
+      <c r="O41">
         <v>18.7</v>
       </c>
-      <c r="O41">
-        <v>18.8</v>
-      </c>
       <c r="P41">
-        <v>101500</v>
+        <v>20100</v>
       </c>
     </row>
     <row r="42">
@@ -2117,19 +2117,19 @@
         <v>51.5</v>
       </c>
       <c r="D42">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E42">
-        <v>-0.9615384615384616</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F42">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="G42">
         <v>52</v>
       </c>
       <c r="H42">
-        <v>51.25</v>
+        <v>50.5</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2138,22 +2138,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>837619</v>
+        <v>2419856</v>
       </c>
       <c r="L42">
-        <v>43140.9105</v>
+        <v>124190.05275</v>
       </c>
       <c r="M42">
-        <v>221800</v>
+        <v>307500</v>
       </c>
       <c r="N42">
-        <v>51.25</v>
+        <v>51.5</v>
       </c>
       <c r="O42">
-        <v>51.5</v>
+        <v>51.75</v>
       </c>
       <c r="P42">
-        <v>67600</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="43">
@@ -2164,46 +2164,46 @@
         <v>-</v>
       </c>
       <c r="C43">
+        <v>33.25</v>
+      </c>
+      <c r="D43">
+        <v>-0.25</v>
+      </c>
+      <c r="E43">
+        <v>-0.746268656716418</v>
+      </c>
+      <c r="F43">
+        <v>33.5</v>
+      </c>
+      <c r="G43">
         <v>33.75</v>
       </c>
-      <c r="D43">
-        <v>0.25</v>
-      </c>
-      <c r="E43">
-        <v>0.746268656716418</v>
-      </c>
-      <c r="F43">
-        <v>33.75</v>
-      </c>
-      <c r="G43">
-        <v>34</v>
-      </c>
       <c r="H43">
+        <v>33</v>
+      </c>
+      <c r="I43">
+        <v>374700</v>
+      </c>
+      <c r="J43">
+        <v>12458.775</v>
+      </c>
+      <c r="K43">
+        <v>26462523</v>
+      </c>
+      <c r="L43">
+        <v>882109.52025</v>
+      </c>
+      <c r="M43">
+        <v>3142800</v>
+      </c>
+      <c r="N43">
         <v>33.25</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>7461410</v>
-      </c>
-      <c r="L43">
-        <v>252144.407</v>
-      </c>
-      <c r="M43">
-        <v>1659400</v>
-      </c>
-      <c r="N43">
-        <v>33.75</v>
-      </c>
       <c r="O43">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="P43">
-        <v>1891500</v>
+        <v>2900500</v>
       </c>
     </row>
     <row r="44">
@@ -2214,46 +2214,46 @@
         <v>-</v>
       </c>
       <c r="C44">
+        <v>22.3</v>
+      </c>
+      <c r="D44">
+        <v>-0.2</v>
+      </c>
+      <c r="E44">
+        <v>-0.8888888888888888</v>
+      </c>
+      <c r="F44">
         <v>22.5</v>
       </c>
-      <c r="D44">
-        <v>0.1</v>
-      </c>
-      <c r="E44">
-        <v>0.44642857142857145</v>
-      </c>
-      <c r="F44">
+      <c r="G44">
+        <v>22.5</v>
+      </c>
+      <c r="H44">
+        <v>22.3</v>
+      </c>
+      <c r="I44">
+        <v>87500</v>
+      </c>
+      <c r="J44">
+        <v>1951.25</v>
+      </c>
+      <c r="K44">
+        <v>10067522</v>
+      </c>
+      <c r="L44">
+        <v>225402.4148</v>
+      </c>
+      <c r="M44">
+        <v>2745000</v>
+      </c>
+      <c r="N44">
+        <v>22.3</v>
+      </c>
+      <c r="O44">
         <v>22.4</v>
       </c>
-      <c r="G44">
-        <v>22.7</v>
-      </c>
-      <c r="H44">
-        <v>22.4</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>5808000</v>
-      </c>
-      <c r="L44">
-        <v>131181.3141</v>
-      </c>
-      <c r="M44">
-        <v>1419600</v>
-      </c>
-      <c r="N44">
-        <v>22.5</v>
-      </c>
-      <c r="O44">
-        <v>22.6</v>
-      </c>
       <c r="P44">
-        <v>333500</v>
+        <v>658200</v>
       </c>
     </row>
     <row r="45">
@@ -2264,13 +2264,13 @@
         <v>-</v>
       </c>
       <c r="C45">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="D45">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E45">
-        <v>-0.8771929824561403</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F45">
         <v>28.25</v>
@@ -2279,7 +2279,7 @@
         <v>28.5</v>
       </c>
       <c r="H45">
-        <v>28.25</v>
+        <v>28</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2288,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>1108746</v>
+        <v>5471542</v>
       </c>
       <c r="L45">
-        <v>31330.526</v>
+        <v>154774.204</v>
       </c>
       <c r="M45">
-        <v>639800</v>
+        <v>760700</v>
       </c>
       <c r="N45">
         <v>28.25</v>
@@ -2303,7 +2303,7 @@
         <v>28.5</v>
       </c>
       <c r="P45">
-        <v>1398300</v>
+        <v>714100</v>
       </c>
     </row>
     <row r="46">
@@ -2314,16 +2314,16 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>-0.7633587786259542</v>
       </c>
       <c r="F46">
-        <v>33</v>
+        <v>32.75</v>
       </c>
       <c r="G46">
         <v>33</v>
@@ -2338,22 +2338,22 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>37092275</v>
+        <v>33729036</v>
       </c>
       <c r="L46">
-        <v>1217492.49675</v>
+        <v>1100507.0125</v>
       </c>
       <c r="M46">
-        <v>13678200</v>
+        <v>13937300</v>
       </c>
       <c r="N46">
+        <v>32.5</v>
+      </c>
+      <c r="O46">
         <v>32.75</v>
       </c>
-      <c r="O46">
-        <v>33</v>
-      </c>
       <c r="P46">
-        <v>10779800</v>
+        <v>1785800</v>
       </c>
     </row>
     <row r="47">
@@ -2364,46 +2364,46 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D47">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>-2.3529411764705883</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="F47">
-        <v>169.5</v>
+        <v>164</v>
       </c>
       <c r="G47">
-        <v>169.5</v>
+        <v>165.5</v>
       </c>
       <c r="H47">
+        <v>164</v>
+      </c>
+      <c r="I47">
+        <v>160000</v>
+      </c>
+      <c r="J47">
+        <v>26240</v>
+      </c>
+      <c r="K47">
+        <v>15544249</v>
+      </c>
+      <c r="L47">
+        <v>2560725.5295</v>
+      </c>
+      <c r="M47">
+        <v>810500</v>
+      </c>
+      <c r="N47">
         <v>164.5</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>20392736</v>
-      </c>
-      <c r="L47">
-        <v>3387949.05</v>
-      </c>
-      <c r="M47">
-        <v>773000</v>
-      </c>
-      <c r="N47">
-        <v>166</v>
-      </c>
       <c r="O47">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="P47">
-        <v>252600</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="48">
@@ -2414,16 +2414,16 @@
         <v>-</v>
       </c>
       <c r="C48">
-        <v>49.5</v>
+        <v>49.75</v>
       </c>
       <c r="D48">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E48">
-        <v>-0.5025125628140703</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="F48">
-        <v>50</v>
+        <v>49.25</v>
       </c>
       <c r="G48">
         <v>50</v>
@@ -2438,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>3436893</v>
+        <v>9366275</v>
       </c>
       <c r="L48">
-        <v>170335.43975</v>
+        <v>464101.732</v>
       </c>
       <c r="M48">
-        <v>618200</v>
+        <v>1252000</v>
       </c>
       <c r="N48">
         <v>49.5</v>
@@ -2453,7 +2453,7 @@
         <v>49.75</v>
       </c>
       <c r="P48">
-        <v>275200</v>
+        <v>526900</v>
       </c>
     </row>
     <row r="49">
@@ -2464,46 +2464,46 @@
         <v>-</v>
       </c>
       <c r="C49">
-        <v>43.25</v>
+        <v>42.5</v>
       </c>
       <c r="D49">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E49">
-        <v>0.5813953488372093</v>
+        <v>-0.5847953216374269</v>
       </c>
       <c r="F49">
+        <v>42.5</v>
+      </c>
+      <c r="G49">
         <v>42.75</v>
       </c>
-      <c r="G49">
-        <v>43.25</v>
-      </c>
       <c r="H49">
+        <v>42.25</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>2231778</v>
+      </c>
+      <c r="L49">
+        <v>94917.6095</v>
+      </c>
+      <c r="M49">
+        <v>242100</v>
+      </c>
+      <c r="N49">
+        <v>42.5</v>
+      </c>
+      <c r="O49">
         <v>42.75</v>
       </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>1069275</v>
-      </c>
-      <c r="L49">
-        <v>45962.1565</v>
-      </c>
-      <c r="M49">
-        <v>169400</v>
-      </c>
-      <c r="N49">
-        <v>43</v>
-      </c>
-      <c r="O49">
-        <v>43.25</v>
-      </c>
       <c r="P49">
-        <v>433700</v>
+        <v>159700</v>
       </c>
     </row>
     <row r="50">
@@ -2514,46 +2514,46 @@
         <v>-</v>
       </c>
       <c r="C50">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="D50">
         <v>0.1</v>
       </c>
       <c r="E50">
-        <v>0.7751937984496124</v>
+        <v>0.78125</v>
       </c>
       <c r="F50">
+        <v>12.8</v>
+      </c>
+      <c r="G50">
         <v>13</v>
       </c>
-      <c r="G50">
-        <v>13.1</v>
-      </c>
       <c r="H50">
+        <v>12.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>3377331</v>
+      </c>
+      <c r="L50">
+        <v>43600.9581</v>
+      </c>
+      <c r="M50">
+        <v>334900</v>
+      </c>
+      <c r="N50">
+        <v>12.8</v>
+      </c>
+      <c r="O50">
         <v>12.9</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>688022</v>
-      </c>
-      <c r="L50">
-        <v>8931.6222</v>
-      </c>
-      <c r="M50">
-        <v>214500</v>
-      </c>
-      <c r="N50">
-        <v>12.9</v>
-      </c>
-      <c r="O50">
-        <v>13</v>
-      </c>
       <c r="P50">
-        <v>327700</v>
+        <v>419300</v>
       </c>
     </row>
     <row r="51">
@@ -2567,19 +2567,19 @@
         <v>31</v>
       </c>
       <c r="D51">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>2.479338842975207</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G51">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="H51">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2588,13 +2588,13 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>1326990</v>
+        <v>1864108</v>
       </c>
       <c r="L51">
-        <v>40796.9215</v>
+        <v>57752.77575</v>
       </c>
       <c r="M51">
-        <v>209300</v>
+        <v>385200</v>
       </c>
       <c r="N51">
         <v>30.75</v>
@@ -2603,7 +2603,7 @@
         <v>31</v>
       </c>
       <c r="P51">
-        <v>536800</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="52">
@@ -2614,22 +2614,22 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="D52">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E52">
-        <v>0.8849557522123894</v>
+        <v>-1.7543859649122806</v>
       </c>
       <c r="F52">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="H52">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>16569929</v>
+        <v>9903903</v>
       </c>
       <c r="L52">
-        <v>96573.90879999999</v>
+        <v>56251.202</v>
       </c>
       <c r="M52">
-        <v>692300</v>
+        <v>643900</v>
       </c>
       <c r="N52">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O52">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P52">
-        <v>145200</v>
+        <v>1186400</v>
       </c>
     </row>
     <row r="53">
@@ -2664,46 +2664,46 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="D53">
         <v>-0.5</v>
       </c>
       <c r="E53">
-        <v>-0.47619047619047616</v>
+        <v>-0.4807692307692308</v>
       </c>
       <c r="F53">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="G53">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="H53">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>30400</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>3146.4</v>
       </c>
       <c r="K53">
-        <v>684901</v>
+        <v>7684973</v>
       </c>
       <c r="L53">
-        <v>71852.403</v>
+        <v>791786.1195</v>
       </c>
       <c r="M53">
-        <v>1115600</v>
+        <v>639400</v>
       </c>
       <c r="N53">
-        <v>104.5</v>
+        <v>103</v>
       </c>
       <c r="O53">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="P53">
-        <v>1364400</v>
+        <v>169900</v>
       </c>
     </row>
     <row r="54">
@@ -2714,46 +2714,46 @@
         <v>-</v>
       </c>
       <c r="C54">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54">
-        <v>0.2958579881656805</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="F54">
         <v>337</v>
       </c>
       <c r="G54">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H54">
+        <v>336</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>2304687</v>
+      </c>
+      <c r="L54">
+        <v>778502.554</v>
+      </c>
+      <c r="M54">
+        <v>487000</v>
+      </c>
+      <c r="N54">
         <v>337</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>1875224</v>
-      </c>
-      <c r="L54">
-        <v>634175.786</v>
-      </c>
-      <c r="M54">
-        <v>111400</v>
-      </c>
-      <c r="N54">
+      <c r="O54">
         <v>338</v>
       </c>
-      <c r="O54">
-        <v>339</v>
-      </c>
       <c r="P54">
-        <v>98600</v>
+        <v>211800</v>
       </c>
     </row>
     <row r="55">
@@ -2764,22 +2764,22 @@
         <v>-</v>
       </c>
       <c r="C55">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="D55">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E55">
-        <v>-0.31347962382445144</v>
+        <v>-0.6309148264984227</v>
       </c>
       <c r="F55">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="G55">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="H55">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>173063</v>
+        <v>417258</v>
       </c>
       <c r="L55">
-        <v>27487.9135</v>
+        <v>65712.735</v>
       </c>
       <c r="M55">
-        <v>500</v>
+        <v>14800</v>
       </c>
       <c r="N55">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O55">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="P55">
-        <v>1600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="56">
@@ -2817,10 +2817,10 @@
         <v>53.5</v>
       </c>
       <c r="D56">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.4694835680751174</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>53.5</v>
@@ -2829,22 +2829,22 @@
         <v>53.75</v>
       </c>
       <c r="H56">
-        <v>53.25</v>
+        <v>53</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>936.25</v>
       </c>
       <c r="K56">
-        <v>1702870</v>
+        <v>5797609</v>
       </c>
       <c r="L56">
-        <v>91093.57375</v>
+        <v>309590.9925</v>
       </c>
       <c r="M56">
-        <v>739000</v>
+        <v>199300</v>
       </c>
       <c r="N56">
         <v>53.25</v>
@@ -2853,7 +2853,7 @@
         <v>53.5</v>
       </c>
       <c r="P56">
-        <v>609700</v>
+        <v>145700</v>
       </c>
     </row>
     <row r="57">
@@ -2864,22 +2864,22 @@
         <v>-</v>
       </c>
       <c r="C57">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="D57">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="E57">
-        <v>-2.6315789473684212</v>
+        <v>2.7027027027027026</v>
       </c>
       <c r="F57">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G57">
         <v>11.5</v>
       </c>
       <c r="H57">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2888,22 +2888,22 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>16051623</v>
+        <v>30955605</v>
       </c>
       <c r="L57">
-        <v>179251.83419999998</v>
+        <v>353231.8855</v>
       </c>
       <c r="M57">
-        <v>1518500</v>
+        <v>2846200</v>
       </c>
       <c r="N57">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="O57">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="P57">
-        <v>374700</v>
+        <v>184900</v>
       </c>
     </row>
     <row r="58">
@@ -2914,46 +2914,46 @@
         <v>-</v>
       </c>
       <c r="C58">
+        <v>9.95</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>9.95</v>
+      </c>
+      <c r="G58">
         <v>10</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
+      <c r="H58">
+        <v>9.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>1153621</v>
+      </c>
+      <c r="L58">
+        <v>11490.54515</v>
+      </c>
+      <c r="M58">
+        <v>117100</v>
+      </c>
+      <c r="N58">
+        <v>9.95</v>
+      </c>
+      <c r="O58">
         <v>10</v>
       </c>
-      <c r="G58">
-        <v>10.1</v>
-      </c>
-      <c r="H58">
-        <v>10</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>441648</v>
-      </c>
-      <c r="L58">
-        <v>4417.4496</v>
-      </c>
-      <c r="M58">
-        <v>45100</v>
-      </c>
-      <c r="N58">
-        <v>10</v>
-      </c>
-      <c r="O58">
-        <v>10.1</v>
-      </c>
       <c r="P58">
-        <v>324500</v>
+        <v>135900</v>
       </c>
     </row>
     <row r="59">
@@ -2964,22 +2964,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="D59">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E59">
-        <v>-0.8771929824561403</v>
+        <v>2.7027027027027026</v>
       </c>
       <c r="F59">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="G59">
         <v>11.6</v>
       </c>
       <c r="H59">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>13236816</v>
+        <v>26522526</v>
       </c>
       <c r="L59">
-        <v>150250.6619</v>
+        <v>302055.1235</v>
       </c>
       <c r="M59">
-        <v>847700</v>
+        <v>1124000</v>
       </c>
       <c r="N59">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="O59">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="P59">
-        <v>280100</v>
+        <v>556600</v>
       </c>
     </row>
     <row r="60">
@@ -3014,7 +3014,7 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3023,37 +3023,37 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="G60">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H60">
+        <v>0.62</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>42611749</v>
+      </c>
+      <c r="L60">
+        <v>26886.48375</v>
+      </c>
+      <c r="M60">
+        <v>9893600</v>
+      </c>
+      <c r="N60">
         <v>0.63</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>68803870</v>
-      </c>
-      <c r="L60">
-        <v>44046.87118</v>
-      </c>
-      <c r="M60">
-        <v>2583200</v>
-      </c>
-      <c r="N60">
+      <c r="O60">
         <v>0.64</v>
       </c>
-      <c r="O60">
-        <v>0.65</v>
-      </c>
       <c r="P60">
-        <v>38593700</v>
+        <v>18546100</v>
       </c>
     </row>
     <row r="61">
@@ -3064,23 +3064,23 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="D61">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>1.694915254237288</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="G61">
+        <v>18.5</v>
+      </c>
+      <c r="H61">
         <v>18.2</v>
       </c>
-      <c r="H61">
-        <v>17.7</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -3088,22 +3088,22 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>4474887</v>
+        <v>6759324</v>
       </c>
       <c r="L61">
-        <v>80421.125</v>
+        <v>123685.3796</v>
       </c>
       <c r="M61">
-        <v>846800</v>
+        <v>96000</v>
       </c>
       <c r="N61">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="O61">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="P61">
-        <v>323200</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="62">
@@ -3114,22 +3114,22 @@
         <v>-</v>
       </c>
       <c r="C62">
+        <v>16.1</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>16.1</v>
+      </c>
+      <c r="G62">
         <v>16.2</v>
       </c>
-      <c r="D62">
-        <v>0.1</v>
-      </c>
-      <c r="E62">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F62">
-        <v>16.2</v>
-      </c>
-      <c r="G62">
-        <v>16.3</v>
-      </c>
       <c r="H62">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3138,13 +3138,13 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>2458468</v>
+        <v>5819119</v>
       </c>
       <c r="L62">
-        <v>39842.401600000005</v>
+        <v>93254.035</v>
       </c>
       <c r="M62">
-        <v>339400</v>
+        <v>71300</v>
       </c>
       <c r="N62">
         <v>16.1</v>
@@ -3153,7 +3153,7 @@
         <v>16.2</v>
       </c>
       <c r="P62">
-        <v>115300</v>
+        <v>308200</v>
       </c>
     </row>
     <row r="63">
@@ -3164,16 +3164,16 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>57.25</v>
+        <v>57</v>
       </c>
       <c r="D63">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E63">
-        <v>-0.8658008658008658</v>
+        <v>-0.4366812227074236</v>
       </c>
       <c r="F63">
-        <v>57.75</v>
+        <v>57.5</v>
       </c>
       <c r="G63">
         <v>58</v>
@@ -3188,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>7565247</v>
+        <v>9125904</v>
       </c>
       <c r="L63">
-        <v>432750.8315</v>
+        <v>523788.4305</v>
       </c>
       <c r="M63">
-        <v>467600</v>
+        <v>10400</v>
       </c>
       <c r="N63">
         <v>57</v>
@@ -3203,7 +3203,7 @@
         <v>57.25</v>
       </c>
       <c r="P63">
-        <v>722600</v>
+        <v>552800</v>
       </c>
     </row>
     <row r="64">
@@ -3214,22 +3214,22 @@
         <v>-</v>
       </c>
       <c r="C64">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="D64">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E64">
-        <v>-0.8264462809917356</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F64">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="G64">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="H64">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3238,22 +3238,22 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>1779100</v>
+        <v>2418600</v>
       </c>
       <c r="L64">
-        <v>2153.838</v>
+        <v>2811.27308</v>
       </c>
       <c r="M64">
-        <v>779800</v>
+        <v>213000</v>
       </c>
       <c r="N64">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="O64">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P64">
-        <v>339700</v>
+        <v>183700</v>
       </c>
     </row>
     <row r="65">
@@ -3267,43 +3267,43 @@
         <v>16.2</v>
       </c>
       <c r="D65">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>0.6211180124223602</v>
+        <v>0</v>
       </c>
       <c r="F65">
+        <v>16.3</v>
+      </c>
+      <c r="G65">
+        <v>16.4</v>
+      </c>
+      <c r="H65">
         <v>16.1</v>
       </c>
-      <c r="G65">
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>16289493</v>
+      </c>
+      <c r="L65">
+        <v>264277.7181</v>
+      </c>
+      <c r="M65">
+        <v>1328900</v>
+      </c>
+      <c r="N65">
         <v>16.2</v>
       </c>
-      <c r="H65">
-        <v>16</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>4613789</v>
-      </c>
-      <c r="L65">
-        <v>74294.3007</v>
-      </c>
-      <c r="M65">
-        <v>1120400</v>
-      </c>
-      <c r="N65">
-        <v>16.1</v>
-      </c>
       <c r="O65">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P65">
-        <v>2225000</v>
+        <v>1582700</v>
       </c>
     </row>
     <row r="66">
@@ -3317,19 +3317,19 @@
         <v>5.55</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>-0.8928571428571429</v>
       </c>
       <c r="F66">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G66">
         <v>5.6</v>
       </c>
       <c r="H66">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>356500</v>
+        <v>746211</v>
       </c>
       <c r="L66">
-        <v>1968.645</v>
+        <v>4115.07705</v>
       </c>
       <c r="M66">
-        <v>226000</v>
+        <v>700</v>
       </c>
       <c r="N66">
         <v>5.5</v>
@@ -3353,7 +3353,7 @@
         <v>5.55</v>
       </c>
       <c r="P66">
-        <v>38200</v>
+        <v>79200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (2).xlsx
+++ b/Excel/StockQuotation (2).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:29:43</v>
+        <v>08/02/23 20:05:34</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1008.43</v>
+        <v>1004.66</v>
       </c>
       <c r="B7" t="str">
-        <v>0.39 (0.0386%)</v>
+        <v>-3.77 (-0.3738%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1010.7</v>
+        <v>1013.31</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1002.49</v>
+        <v>1003.5</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>699120426</v>
+        <v>981762814</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>19003898633.81</v>
+        <v>19208568059.41</v>
       </c>
     </row>
     <row r="9">
@@ -514,46 +514,46 @@
         <v>-</v>
       </c>
       <c r="C10">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D10">
         <v>-0.1</v>
       </c>
       <c r="E10">
-        <v>-0.7692307692307693</v>
+        <v>-0.7751937984496124</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="G10">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="H10">
+        <v>12.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>268667</v>
+      </c>
+      <c r="L10">
+        <v>3443.391</v>
+      </c>
+      <c r="M10">
+        <v>26100</v>
+      </c>
+      <c r="N10">
+        <v>12.7</v>
+      </c>
+      <c r="O10">
         <v>12.8</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>296417</v>
-      </c>
-      <c r="L10">
-        <v>3835.5916</v>
-      </c>
-      <c r="M10">
-        <v>86000</v>
-      </c>
-      <c r="N10">
-        <v>12.8</v>
-      </c>
-      <c r="O10">
-        <v>12.9</v>
-      </c>
       <c r="P10">
-        <v>27100</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="11">
@@ -573,13 +573,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="G11">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="H11">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -588,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>6175226</v>
+        <v>7211455</v>
       </c>
       <c r="L11">
-        <v>124102.2675</v>
+        <v>146060.62269999998</v>
       </c>
       <c r="M11">
-        <v>171800</v>
+        <v>470200</v>
       </c>
       <c r="N11">
         <v>20.1</v>
@@ -603,7 +603,7 @@
         <v>20.2</v>
       </c>
       <c r="P11">
-        <v>143600</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="12">
@@ -614,46 +614,46 @@
         <v>-</v>
       </c>
       <c r="C12">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E12">
-        <v>-0.8849557522123894</v>
+        <v>-1.7857142857142858</v>
       </c>
       <c r="F12">
         <v>11.3</v>
       </c>
       <c r="G12">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="H12">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="I12">
-        <v>100000</v>
+        <v>9768400</v>
       </c>
       <c r="J12">
-        <v>1134</v>
+        <v>107468.6</v>
       </c>
       <c r="K12">
-        <v>161516144</v>
+        <v>136003874</v>
       </c>
       <c r="L12">
-        <v>1831534.3802</v>
+        <v>1507824.1778</v>
       </c>
       <c r="M12">
-        <v>23883600</v>
+        <v>16196200</v>
       </c>
       <c r="N12">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O12">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="P12">
-        <v>772100</v>
+        <v>6055600</v>
       </c>
     </row>
     <row r="13">
@@ -664,37 +664,37 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>160.5</v>
+        <v>160</v>
       </c>
       <c r="D13">
         <v>-0.5</v>
       </c>
       <c r="E13">
-        <v>-0.3105590062111801</v>
+        <v>-0.3115264797507788</v>
       </c>
       <c r="F13">
-        <v>161.5</v>
+        <v>160</v>
       </c>
       <c r="G13">
-        <v>161.5</v>
+        <v>161</v>
       </c>
       <c r="H13">
         <v>160</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>25680</v>
       </c>
       <c r="K13">
-        <v>3101777</v>
+        <v>3694629</v>
       </c>
       <c r="L13">
-        <v>497468.5115</v>
+        <v>592696.122</v>
       </c>
       <c r="M13">
-        <v>756800</v>
+        <v>505300</v>
       </c>
       <c r="N13">
         <v>160</v>
@@ -703,7 +703,7 @@
         <v>160.5</v>
       </c>
       <c r="P13">
-        <v>235000</v>
+        <v>189400</v>
       </c>
     </row>
     <row r="14">
@@ -714,19 +714,19 @@
         <v>-</v>
       </c>
       <c r="C14">
+        <v>21</v>
+      </c>
+      <c r="D14">
+        <v>-0.1</v>
+      </c>
+      <c r="E14">
+        <v>-0.47393364928909953</v>
+      </c>
+      <c r="F14">
         <v>21.1</v>
       </c>
-      <c r="D14">
-        <v>-0.2</v>
-      </c>
-      <c r="E14">
-        <v>-0.9389671361502347</v>
-      </c>
-      <c r="F14">
-        <v>21.3</v>
-      </c>
       <c r="G14">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H14">
         <v>20.9</v>
@@ -738,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>11021734</v>
+        <v>3154617</v>
       </c>
       <c r="L14">
-        <v>232419.2244</v>
+        <v>66212.80129999999</v>
       </c>
       <c r="M14">
-        <v>2048300</v>
+        <v>962800</v>
       </c>
       <c r="N14">
         <v>21</v>
@@ -753,7 +753,7 @@
         <v>21.1</v>
       </c>
       <c r="P14">
-        <v>189800</v>
+        <v>261500</v>
       </c>
     </row>
     <row r="15">
@@ -767,19 +767,19 @@
         <v>35.5</v>
       </c>
       <c r="D15">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>-1.3888888888888888</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="G15">
-        <v>36</v>
+        <v>36.25</v>
       </c>
       <c r="H15">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5801589</v>
+        <v>4793027</v>
       </c>
       <c r="L15">
-        <v>206626.30275</v>
+        <v>171218.572</v>
       </c>
       <c r="M15">
-        <v>767100</v>
+        <v>261300</v>
       </c>
       <c r="N15">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
       <c r="O15">
-        <v>35.5</v>
+        <v>35.75</v>
       </c>
       <c r="P15">
-        <v>21000</v>
+        <v>399600</v>
       </c>
     </row>
     <row r="16">
@@ -823,37 +823,37 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>10.1</v>
       </c>
       <c r="H16">
+        <v>9.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>2617235</v>
+      </c>
+      <c r="L16">
+        <v>26131.1178</v>
+      </c>
+      <c r="M16">
+        <v>102800</v>
+      </c>
+      <c r="N16">
+        <v>9.95</v>
+      </c>
+      <c r="O16">
         <v>10</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>1404493</v>
-      </c>
-      <c r="L16">
-        <v>14074.1795</v>
-      </c>
-      <c r="M16">
-        <v>640200</v>
-      </c>
-      <c r="N16">
-        <v>10</v>
-      </c>
-      <c r="O16">
-        <v>10.1</v>
-      </c>
       <c r="P16">
-        <v>895700</v>
+        <v>137100</v>
       </c>
     </row>
     <row r="17">
@@ -867,43 +867,43 @@
         <v>29.5</v>
       </c>
       <c r="D17">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.8403361344537815</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="G17">
         <v>30</v>
       </c>
       <c r="H17">
+        <v>29.25</v>
+      </c>
+      <c r="I17">
+        <v>570000</v>
+      </c>
+      <c r="J17">
+        <v>16815</v>
+      </c>
+      <c r="K17">
+        <v>27537710</v>
+      </c>
+      <c r="L17">
+        <v>814225.86</v>
+      </c>
+      <c r="M17">
+        <v>7226400</v>
+      </c>
+      <c r="N17">
+        <v>29.25</v>
+      </c>
+      <c r="O17">
         <v>29.5</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>21781654</v>
-      </c>
-      <c r="L17">
-        <v>646621.64125</v>
-      </c>
-      <c r="M17">
-        <v>9700400</v>
-      </c>
-      <c r="N17">
-        <v>29.5</v>
-      </c>
-      <c r="O17">
-        <v>29.75</v>
-      </c>
       <c r="P17">
-        <v>1863000</v>
+        <v>2960000</v>
       </c>
     </row>
     <row r="18">
@@ -914,16 +914,16 @@
         <v>-</v>
       </c>
       <c r="C18">
+        <v>10.2</v>
+      </c>
+      <c r="D18">
+        <v>-0.1</v>
+      </c>
+      <c r="E18">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F18">
         <v>10.3</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>10.2</v>
       </c>
       <c r="G18">
         <v>10.4</v>
@@ -938,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>321738</v>
+        <v>177824</v>
       </c>
       <c r="L18">
-        <v>3312.4498</v>
+        <v>1825.4173</v>
       </c>
       <c r="M18">
-        <v>918600</v>
+        <v>895700</v>
       </c>
       <c r="N18">
         <v>10.2</v>
@@ -953,7 +953,7 @@
         <v>10.3</v>
       </c>
       <c r="P18">
-        <v>62400</v>
+        <v>104200</v>
       </c>
     </row>
     <row r="19">
@@ -964,46 +964,46 @@
         <v>-</v>
       </c>
       <c r="C19">
+        <v>40.25</v>
+      </c>
+      <c r="D19">
+        <v>-0.5</v>
+      </c>
+      <c r="E19">
+        <v>-1.2269938650306749</v>
+      </c>
+      <c r="F19">
         <v>40.75</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2.5157232704402515</v>
-      </c>
-      <c r="F19">
+      <c r="G19">
+        <v>41</v>
+      </c>
+      <c r="H19">
         <v>40</v>
       </c>
-      <c r="G19">
-        <v>40.75</v>
-      </c>
-      <c r="H19">
-        <v>39.75</v>
-      </c>
       <c r="I19">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>982.1</v>
       </c>
       <c r="K19">
-        <v>9101197</v>
+        <v>3631038</v>
       </c>
       <c r="L19">
-        <v>365517.13</v>
+        <v>146463.26475</v>
       </c>
       <c r="M19">
-        <v>464700</v>
+        <v>916000</v>
       </c>
       <c r="N19">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="O19">
-        <v>40.75</v>
+        <v>40.25</v>
       </c>
       <c r="P19">
-        <v>724300</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="20">
@@ -1017,43 +1017,43 @@
         <v>214</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.46511627906976744</v>
+        <v>0</v>
       </c>
       <c r="F20">
+        <v>215</v>
+      </c>
+      <c r="G20">
+        <v>216</v>
+      </c>
+      <c r="H20">
+        <v>212</v>
+      </c>
+      <c r="I20">
+        <v>4600</v>
+      </c>
+      <c r="J20">
+        <v>984.4</v>
+      </c>
+      <c r="K20">
+        <v>2703727</v>
+      </c>
+      <c r="L20">
+        <v>577269.675</v>
+      </c>
+      <c r="M20">
+        <v>68600</v>
+      </c>
+      <c r="N20">
+        <v>213</v>
+      </c>
+      <c r="O20">
         <v>214</v>
       </c>
-      <c r="G20">
-        <v>215</v>
-      </c>
-      <c r="H20">
-        <v>211</v>
-      </c>
-      <c r="I20">
-        <v>13600</v>
-      </c>
-      <c r="J20">
-        <v>2910.4</v>
-      </c>
-      <c r="K20">
-        <v>2593682</v>
-      </c>
-      <c r="L20">
-        <v>553752.373</v>
-      </c>
-      <c r="M20">
-        <v>315500</v>
-      </c>
-      <c r="N20">
-        <v>214</v>
-      </c>
-      <c r="O20">
-        <v>215</v>
-      </c>
       <c r="P20">
-        <v>204300</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="21">
@@ -1064,22 +1064,22 @@
         <v>-</v>
       </c>
       <c r="C21">
+        <v>38.75</v>
+      </c>
+      <c r="D21">
+        <v>0.25</v>
+      </c>
+      <c r="E21">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="F21">
         <v>38.5</v>
       </c>
-      <c r="D21">
-        <v>0.5</v>
-      </c>
-      <c r="E21">
-        <v>1.3157894736842106</v>
-      </c>
-      <c r="F21">
-        <v>38.25</v>
-      </c>
       <c r="G21">
-        <v>38.75</v>
+        <v>39.5</v>
       </c>
       <c r="H21">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>4774943</v>
+        <v>10373715</v>
       </c>
       <c r="L21">
-        <v>182526.64975</v>
+        <v>403408.98225</v>
       </c>
       <c r="M21">
-        <v>374200</v>
+        <v>18100</v>
       </c>
       <c r="N21">
         <v>38.5</v>
@@ -1103,7 +1103,7 @@
         <v>38.75</v>
       </c>
       <c r="P21">
-        <v>403100</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="D22">
         <v>0.1</v>
       </c>
       <c r="E22">
-        <v>0.5882352941176471</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="F22">
         <v>17.1</v>
       </c>
       <c r="G22">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="H22">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>551835</v>
+        <v>1900409</v>
       </c>
       <c r="L22">
-        <v>9361.9499</v>
+        <v>32622.191600000002</v>
       </c>
       <c r="M22">
-        <v>17000</v>
+        <v>86000</v>
       </c>
       <c r="N22">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O22">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P22">
-        <v>228900</v>
+        <v>268500</v>
       </c>
     </row>
     <row r="23">
@@ -1164,46 +1164,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="E23">
-        <v>-0.970873786407767</v>
+        <v>-1.4705882352941178</v>
       </c>
       <c r="F23">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="G23">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="H23">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>8844</v>
       </c>
       <c r="K23">
-        <v>1768116</v>
+        <v>1844304</v>
       </c>
       <c r="L23">
-        <v>180572.946</v>
+        <v>186542.3475</v>
       </c>
       <c r="M23">
-        <v>151600</v>
+        <v>269000</v>
       </c>
       <c r="N23">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="O23">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P23">
-        <v>63900</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="24">
@@ -1217,34 +1217,34 @@
         <v>22.4</v>
       </c>
       <c r="D24">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>-1.3215859030837005</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="G24">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="H24">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="I24">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>5067398</v>
+        <v>3866931</v>
       </c>
       <c r="L24">
-        <v>114296.93509999999</v>
+        <v>86797.80290000001</v>
       </c>
       <c r="M24">
-        <v>600600</v>
+        <v>578100</v>
       </c>
       <c r="N24">
         <v>22.4</v>
@@ -1253,7 +1253,7 @@
         <v>22.5</v>
       </c>
       <c r="P24">
-        <v>71100</v>
+        <v>144400</v>
       </c>
     </row>
     <row r="25">
@@ -1264,46 +1264,46 @@
         <v>-</v>
       </c>
       <c r="C25">
+        <v>4.66</v>
+      </c>
+      <c r="D25">
+        <v>-0.02</v>
+      </c>
+      <c r="E25">
+        <v>-0.42735042735042733</v>
+      </c>
+      <c r="F25">
         <v>4.68</v>
       </c>
-      <c r="D25">
-        <v>0.08</v>
-      </c>
-      <c r="E25">
-        <v>1.7391304347826086</v>
-      </c>
-      <c r="F25">
+      <c r="G25">
+        <v>4.7</v>
+      </c>
+      <c r="H25">
+        <v>4.62</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>12625762</v>
+      </c>
+      <c r="L25">
+        <v>58798.19654</v>
+      </c>
+      <c r="M25">
+        <v>227900</v>
+      </c>
+      <c r="N25">
         <v>4.64</v>
       </c>
-      <c r="G25">
-        <v>4.72</v>
-      </c>
-      <c r="H25">
-        <v>4.6</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>24336619</v>
-      </c>
-      <c r="L25">
-        <v>113698.60182</v>
-      </c>
-      <c r="M25">
-        <v>1189900</v>
-      </c>
-      <c r="N25">
+      <c r="O25">
         <v>4.66</v>
       </c>
-      <c r="O25">
-        <v>4.68</v>
-      </c>
       <c r="P25">
-        <v>359000</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="26">
@@ -1314,46 +1314,46 @@
         <v>-</v>
       </c>
       <c r="C26">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>-1.271186440677966</v>
       </c>
       <c r="F26">
         <v>23.6</v>
       </c>
       <c r="G26">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="H26">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>3472000</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>80897.6</v>
       </c>
       <c r="K26">
-        <v>17028962</v>
+        <v>28889712</v>
       </c>
       <c r="L26">
-        <v>401183.07739999995</v>
+        <v>675575.3047999999</v>
       </c>
       <c r="M26">
-        <v>2056100</v>
+        <v>5431700</v>
       </c>
       <c r="N26">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="O26">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="P26">
-        <v>347500</v>
+        <v>1514900</v>
       </c>
     </row>
     <row r="27">
@@ -1367,19 +1367,19 @@
         <v>44.25</v>
       </c>
       <c r="D27">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>-0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>44.5</v>
+        <v>44.25</v>
       </c>
       <c r="G27">
         <v>44.5</v>
       </c>
       <c r="H27">
-        <v>43.75</v>
+        <v>44</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>10167453</v>
+        <v>11168771</v>
       </c>
       <c r="L27">
-        <v>448185.82275</v>
+        <v>493385.741</v>
       </c>
       <c r="M27">
-        <v>667100</v>
+        <v>947000</v>
       </c>
       <c r="N27">
         <v>44</v>
@@ -1403,7 +1403,7 @@
         <v>44.25</v>
       </c>
       <c r="P27">
-        <v>1198400</v>
+        <v>1021800</v>
       </c>
     </row>
     <row r="28">
@@ -1414,13 +1414,13 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D28">
         <v>-0.05</v>
       </c>
       <c r="E28">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F28">
         <v>8.25</v>
@@ -1429,31 +1429,31 @@
         <v>8.3</v>
       </c>
       <c r="H28">
+        <v>8.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>62782</v>
+      </c>
+      <c r="L28">
+        <v>518.53745</v>
+      </c>
+      <c r="M28">
+        <v>45000</v>
+      </c>
+      <c r="N28">
+        <v>8.2</v>
+      </c>
+      <c r="O28">
         <v>8.25</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>137355</v>
-      </c>
-      <c r="L28">
-        <v>1134.4045</v>
-      </c>
-      <c r="M28">
-        <v>11800</v>
-      </c>
-      <c r="N28">
-        <v>8.25</v>
-      </c>
-      <c r="O28">
-        <v>8.3</v>
-      </c>
       <c r="P28">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="29">
@@ -1464,13 +1464,13 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>172</v>
+        <v>171.5</v>
       </c>
       <c r="D29">
         <v>-0.5</v>
       </c>
       <c r="E29">
-        <v>-0.2898550724637681</v>
+        <v>-0.29069767441860467</v>
       </c>
       <c r="F29">
         <v>172</v>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>944769</v>
+        <v>642855</v>
       </c>
       <c r="L29">
-        <v>162568.3245</v>
+        <v>110252.033</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>10100</v>
       </c>
       <c r="N29">
+        <v>171.5</v>
+      </c>
+      <c r="O29">
         <v>172</v>
       </c>
-      <c r="O29">
-        <v>172.5</v>
-      </c>
       <c r="P29">
-        <v>23000</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="30">
@@ -1514,13 +1514,13 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>-0.4784688995215311</v>
       </c>
       <c r="F30">
         <v>20.9</v>
@@ -1532,28 +1532,28 @@
         <v>20.7</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="K30">
-        <v>11074770</v>
+        <v>8045090</v>
       </c>
       <c r="L30">
-        <v>230826.29940000002</v>
+        <v>167697.2623</v>
       </c>
       <c r="M30">
-        <v>9800</v>
+        <v>797800</v>
       </c>
       <c r="N30">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="O30">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P30">
-        <v>851900</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="31">
@@ -1564,46 +1564,46 @@
         <v>-</v>
       </c>
       <c r="C31">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="D31">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E31">
-        <v>0.7246376811594203</v>
+        <v>-0.7194244604316546</v>
       </c>
       <c r="F31">
-        <v>69</v>
+        <v>69.75</v>
       </c>
       <c r="G31">
         <v>69.75</v>
       </c>
       <c r="H31">
+        <v>68.75</v>
+      </c>
+      <c r="I31">
+        <v>13600</v>
+      </c>
+      <c r="J31">
+        <v>938.4</v>
+      </c>
+      <c r="K31">
+        <v>3744640</v>
+      </c>
+      <c r="L31">
+        <v>258684.2265</v>
+      </c>
+      <c r="M31">
+        <v>422400</v>
+      </c>
+      <c r="N31">
+        <v>68.75</v>
+      </c>
+      <c r="O31">
         <v>69</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>3829162</v>
-      </c>
-      <c r="L31">
-        <v>265731.12725</v>
-      </c>
-      <c r="M31">
-        <v>160600</v>
-      </c>
-      <c r="N31">
-        <v>69.25</v>
-      </c>
-      <c r="O31">
-        <v>69.5</v>
-      </c>
       <c r="P31">
-        <v>41000</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="32">
@@ -1614,46 +1614,46 @@
         <v>-</v>
       </c>
       <c r="C32">
+        <v>53.5</v>
+      </c>
+      <c r="D32">
+        <v>-0.5</v>
+      </c>
+      <c r="E32">
+        <v>-0.9259259259259259</v>
+      </c>
+      <c r="F32">
         <v>54</v>
-      </c>
-      <c r="D32">
-        <v>0.25</v>
-      </c>
-      <c r="E32">
-        <v>0.46511627906976744</v>
-      </c>
-      <c r="F32">
-        <v>53.75</v>
       </c>
       <c r="G32">
         <v>54.25</v>
       </c>
       <c r="H32">
+        <v>53.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>7868410</v>
+      </c>
+      <c r="L32">
+        <v>423202.82</v>
+      </c>
+      <c r="M32">
+        <v>1821500</v>
+      </c>
+      <c r="N32">
+        <v>53.5</v>
+      </c>
+      <c r="O32">
         <v>53.75</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>11502957</v>
-      </c>
-      <c r="L32">
-        <v>620947.3135</v>
-      </c>
-      <c r="M32">
-        <v>3345400</v>
-      </c>
-      <c r="N32">
-        <v>53.75</v>
-      </c>
-      <c r="O32">
-        <v>54</v>
-      </c>
       <c r="P32">
-        <v>190800</v>
+        <v>844100</v>
       </c>
     </row>
     <row r="33">
@@ -1664,46 +1664,46 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="D33">
         <v>-0.04</v>
       </c>
       <c r="E33">
-        <v>-0.8032128514056225</v>
+        <v>-0.8097165991902834</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="G33">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="H33">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="I33">
-        <v>580000</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>2865.2</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>52248036</v>
+        <v>83042776</v>
       </c>
       <c r="L33">
-        <v>259856.6892</v>
+        <v>409026.96532</v>
       </c>
       <c r="M33">
-        <v>7270900</v>
+        <v>6304200</v>
       </c>
       <c r="N33">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="O33">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="P33">
-        <v>43100</v>
+        <v>621200</v>
       </c>
     </row>
     <row r="34">
@@ -1714,22 +1714,22 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="D34">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E34">
-        <v>-0.8</v>
+        <v>-2.4193548387096775</v>
       </c>
       <c r="F34">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="G34">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H34">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>3613668</v>
+        <v>4461052</v>
       </c>
       <c r="L34">
-        <v>45327.817299999995</v>
+        <v>54519.0479</v>
       </c>
       <c r="M34">
-        <v>656600</v>
+        <v>579500</v>
       </c>
       <c r="N34">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="O34">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="P34">
-        <v>15000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
+        <v>72</v>
+      </c>
+      <c r="D35">
+        <v>-0.5</v>
+      </c>
+      <c r="E35">
+        <v>-0.6896551724137931</v>
+      </c>
+      <c r="F35">
         <v>72.5</v>
       </c>
-      <c r="D35">
-        <v>-0.25</v>
-      </c>
-      <c r="E35">
-        <v>-0.3436426116838488</v>
-      </c>
-      <c r="F35">
+      <c r="G35">
         <v>72.75</v>
       </c>
-      <c r="G35">
-        <v>73</v>
-      </c>
       <c r="H35">
-        <v>72.25</v>
+        <v>71.5</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>1572591</v>
+        <v>3001482</v>
       </c>
       <c r="L35">
-        <v>114134.26675</v>
+        <v>215776.429</v>
       </c>
       <c r="M35">
-        <v>25400</v>
+        <v>136700</v>
       </c>
       <c r="N35">
-        <v>72.5</v>
+        <v>71.75</v>
       </c>
       <c r="O35">
-        <v>72.75</v>
+        <v>72</v>
       </c>
       <c r="P35">
-        <v>154600</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="36">
@@ -1814,23 +1814,23 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="D36">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E36">
-        <v>-0.6535947712418301</v>
+        <v>1.9736842105263157</v>
       </c>
       <c r="F36">
+        <v>3.08</v>
+      </c>
+      <c r="G36">
+        <v>3.18</v>
+      </c>
+      <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="G36">
-        <v>3.08</v>
-      </c>
-      <c r="H36">
-        <v>3.04</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>19508263</v>
+        <v>281845700</v>
       </c>
       <c r="L36">
-        <v>59583.11662</v>
+        <v>882113.9228</v>
       </c>
       <c r="M36">
-        <v>10848100</v>
+        <v>7637400</v>
       </c>
       <c r="N36">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="P36">
-        <v>1410300</v>
+        <v>1252800</v>
       </c>
     </row>
     <row r="37">
@@ -1864,46 +1864,46 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>20.4</v>
+      </c>
+      <c r="D37">
+        <v>-0.3</v>
+      </c>
+      <c r="E37">
+        <v>-1.4492753623188406</v>
+      </c>
+      <c r="F37">
         <v>20.7</v>
       </c>
-      <c r="D37">
-        <v>-0.2</v>
-      </c>
-      <c r="E37">
-        <v>-0.9569377990430622</v>
-      </c>
-      <c r="F37">
-        <v>20.8</v>
-      </c>
       <c r="G37">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="H37">
+        <v>19.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>7581343</v>
+      </c>
+      <c r="L37">
+        <v>153631.8931</v>
+      </c>
+      <c r="M37">
+        <v>479600</v>
+      </c>
+      <c r="N37">
+        <v>20.4</v>
+      </c>
+      <c r="O37">
         <v>20.5</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>5033514</v>
-      </c>
-      <c r="L37">
-        <v>104421.0835</v>
-      </c>
-      <c r="M37">
-        <v>167300</v>
-      </c>
-      <c r="N37">
-        <v>20.6</v>
-      </c>
-      <c r="O37">
-        <v>20.7</v>
-      </c>
       <c r="P37">
-        <v>10300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="38">
@@ -1917,13 +1917,13 @@
         <v>143.5</v>
       </c>
       <c r="D38">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="G38">
         <v>144.5</v>
@@ -1932,19 +1932,19 @@
         <v>143.5</v>
       </c>
       <c r="I38">
-        <v>500000</v>
+        <v>268000</v>
       </c>
       <c r="J38">
-        <v>72000</v>
+        <v>38575</v>
       </c>
       <c r="K38">
-        <v>7124224</v>
+        <v>6388329</v>
       </c>
       <c r="L38">
-        <v>1025018.0965</v>
+        <v>918999.6015</v>
       </c>
       <c r="M38">
-        <v>1601200</v>
+        <v>1529100</v>
       </c>
       <c r="N38">
         <v>143.5</v>
@@ -1953,7 +1953,7 @@
         <v>144</v>
       </c>
       <c r="P38">
-        <v>163200</v>
+        <v>117600</v>
       </c>
     </row>
     <row r="39">
@@ -1964,46 +1964,46 @@
         <v>-</v>
       </c>
       <c r="C39">
+        <v>67</v>
+      </c>
+      <c r="D39">
+        <v>-0.5</v>
+      </c>
+      <c r="E39">
+        <v>-0.7407407407407407</v>
+      </c>
+      <c r="F39">
         <v>67.5</v>
       </c>
-      <c r="D39">
-        <v>-1</v>
-      </c>
-      <c r="E39">
-        <v>-1.4598540145985401</v>
-      </c>
-      <c r="F39">
-        <v>68.5</v>
-      </c>
       <c r="G39">
-        <v>68.5</v>
+        <v>67.75</v>
       </c>
       <c r="H39">
+        <v>67</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>6480541</v>
+      </c>
+      <c r="L39">
+        <v>435661.81975</v>
+      </c>
+      <c r="M39">
+        <v>103900</v>
+      </c>
+      <c r="N39">
+        <v>67</v>
+      </c>
+      <c r="O39">
         <v>67.25</v>
       </c>
-      <c r="I39">
-        <v>600000</v>
-      </c>
-      <c r="J39">
-        <v>40500</v>
-      </c>
-      <c r="K39">
-        <v>9986259</v>
-      </c>
-      <c r="L39">
-        <v>675593.27775</v>
-      </c>
-      <c r="M39">
-        <v>688400</v>
-      </c>
-      <c r="N39">
-        <v>67.25</v>
-      </c>
-      <c r="O39">
-        <v>67.5</v>
-      </c>
       <c r="P39">
-        <v>110400</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="40">
@@ -2023,14 +2023,14 @@
         <v>0</v>
       </c>
       <c r="F40">
+        <v>3.72</v>
+      </c>
+      <c r="G40">
+        <v>3.72</v>
+      </c>
+      <c r="H40">
         <v>3.66</v>
       </c>
-      <c r="G40">
-        <v>3.7</v>
-      </c>
-      <c r="H40">
-        <v>3.64</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
@@ -2038,13 +2038,13 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>4525592</v>
+        <v>7537526</v>
       </c>
       <c r="L40">
-        <v>16602.01504</v>
+        <v>27784.93184</v>
       </c>
       <c r="M40">
-        <v>711200</v>
+        <v>163200</v>
       </c>
       <c r="N40">
         <v>3.66</v>
@@ -2053,7 +2053,7 @@
         <v>3.68</v>
       </c>
       <c r="P40">
-        <v>86300</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="41">
@@ -2064,19 +2064,19 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D41">
         <v>-0.2</v>
       </c>
       <c r="E41">
-        <v>-1.0638297872340425</v>
+        <v>-1.075268817204301</v>
       </c>
       <c r="F41">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="G41">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="H41">
         <v>18.4</v>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>1235687</v>
+        <v>2692783</v>
       </c>
       <c r="L41">
-        <v>23003.4544</v>
+        <v>50277.9519</v>
       </c>
       <c r="M41">
-        <v>122700</v>
+        <v>107600</v>
       </c>
       <c r="N41">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="O41">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P41">
-        <v>20100</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="42">
@@ -2114,22 +2114,22 @@
         <v>-</v>
       </c>
       <c r="C42">
+        <v>50.75</v>
+      </c>
+      <c r="D42">
+        <v>-0.75</v>
+      </c>
+      <c r="E42">
+        <v>-1.4563106796116505</v>
+      </c>
+      <c r="F42">
         <v>51.5</v>
-      </c>
-      <c r="D42">
-        <v>-0.25</v>
-      </c>
-      <c r="E42">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F42">
-        <v>51.75</v>
       </c>
       <c r="G42">
         <v>52</v>
       </c>
       <c r="H42">
-        <v>50.5</v>
+        <v>50.75</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2138,22 +2138,22 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>2419856</v>
+        <v>1412541</v>
       </c>
       <c r="L42">
-        <v>124190.05275</v>
+        <v>72185.227</v>
       </c>
       <c r="M42">
-        <v>307500</v>
+        <v>103800</v>
       </c>
       <c r="N42">
-        <v>51.5</v>
+        <v>50.75</v>
       </c>
       <c r="O42">
-        <v>51.75</v>
+        <v>51</v>
       </c>
       <c r="P42">
-        <v>22200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="43">
@@ -2164,16 +2164,16 @@
         <v>-</v>
       </c>
       <c r="C43">
+        <v>33.5</v>
+      </c>
+      <c r="D43">
+        <v>0.25</v>
+      </c>
+      <c r="E43">
+        <v>0.7518796992481203</v>
+      </c>
+      <c r="F43">
         <v>33.25</v>
-      </c>
-      <c r="D43">
-        <v>-0.25</v>
-      </c>
-      <c r="E43">
-        <v>-0.746268656716418</v>
-      </c>
-      <c r="F43">
-        <v>33.5</v>
       </c>
       <c r="G43">
         <v>33.75</v>
@@ -2182,19 +2182,19 @@
         <v>33</v>
       </c>
       <c r="I43">
-        <v>374700</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>12458.775</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>26462523</v>
+        <v>16398461</v>
       </c>
       <c r="L43">
-        <v>882109.52025</v>
+        <v>548487.3465</v>
       </c>
       <c r="M43">
-        <v>3142800</v>
+        <v>1959200</v>
       </c>
       <c r="N43">
         <v>33.25</v>
@@ -2203,7 +2203,7 @@
         <v>33.5</v>
       </c>
       <c r="P43">
-        <v>2900500</v>
+        <v>139700</v>
       </c>
     </row>
     <row r="44">
@@ -2214,46 +2214,46 @@
         <v>-</v>
       </c>
       <c r="C44">
+        <v>22.2</v>
+      </c>
+      <c r="D44">
+        <v>-0.1</v>
+      </c>
+      <c r="E44">
+        <v>-0.4484304932735426</v>
+      </c>
+      <c r="F44">
         <v>22.3</v>
       </c>
-      <c r="D44">
-        <v>-0.2</v>
-      </c>
-      <c r="E44">
-        <v>-0.8888888888888888</v>
-      </c>
-      <c r="F44">
-        <v>22.5</v>
-      </c>
       <c r="G44">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="H44">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="I44">
-        <v>87500</v>
+        <v>212000</v>
       </c>
       <c r="J44">
-        <v>1951.25</v>
+        <v>4706.4</v>
       </c>
       <c r="K44">
-        <v>10067522</v>
+        <v>15970538</v>
       </c>
       <c r="L44">
-        <v>225402.4148</v>
+        <v>354820.56639999995</v>
       </c>
       <c r="M44">
-        <v>2745000</v>
+        <v>3590900</v>
       </c>
       <c r="N44">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="O44">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="P44">
-        <v>658200</v>
+        <v>1371000</v>
       </c>
     </row>
     <row r="45">
@@ -2264,37 +2264,37 @@
         <v>-</v>
       </c>
       <c r="C45">
+        <v>28.25</v>
+      </c>
+      <c r="D45">
+        <v>-0.25</v>
+      </c>
+      <c r="E45">
+        <v>-0.8771929824561403</v>
+      </c>
+      <c r="F45">
         <v>28.5</v>
-      </c>
-      <c r="D45">
-        <v>0.25</v>
-      </c>
-      <c r="E45">
-        <v>0.8849557522123894</v>
-      </c>
-      <c r="F45">
-        <v>28.25</v>
       </c>
       <c r="G45">
         <v>28.5</v>
       </c>
       <c r="H45">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>804100</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>22715.825</v>
       </c>
       <c r="K45">
-        <v>5471542</v>
+        <v>2828867</v>
       </c>
       <c r="L45">
-        <v>154774.204</v>
+        <v>79952.18825</v>
       </c>
       <c r="M45">
-        <v>760700</v>
+        <v>1505600</v>
       </c>
       <c r="N45">
         <v>28.25</v>
@@ -2303,7 +2303,7 @@
         <v>28.5</v>
       </c>
       <c r="P45">
-        <v>714100</v>
+        <v>753900</v>
       </c>
     </row>
     <row r="46">
@@ -2314,13 +2314,13 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>32.5</v>
+        <v>32.75</v>
       </c>
       <c r="D46">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E46">
-        <v>-0.7633587786259542</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F46">
         <v>32.75</v>
@@ -2338,13 +2338,13 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>33729036</v>
+        <v>42273305</v>
       </c>
       <c r="L46">
-        <v>1100507.0125</v>
+        <v>1384108.04175</v>
       </c>
       <c r="M46">
-        <v>13937300</v>
+        <v>10710700</v>
       </c>
       <c r="N46">
         <v>32.5</v>
@@ -2353,7 +2353,7 @@
         <v>32.75</v>
       </c>
       <c r="P46">
-        <v>1785800</v>
+        <v>1246100</v>
       </c>
     </row>
     <row r="47">
@@ -2367,34 +2367,34 @@
         <v>165</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0.6097560975609756</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G47">
-        <v>165.5</v>
+        <v>167.5</v>
       </c>
       <c r="H47">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47">
-        <v>160000</v>
+        <v>11900</v>
       </c>
       <c r="J47">
-        <v>26240</v>
+        <v>1963.5</v>
       </c>
       <c r="K47">
-        <v>15544249</v>
+        <v>9754541</v>
       </c>
       <c r="L47">
-        <v>2560725.5295</v>
+        <v>1619306.919</v>
       </c>
       <c r="M47">
-        <v>810500</v>
+        <v>918900</v>
       </c>
       <c r="N47">
         <v>164.5</v>
@@ -2403,7 +2403,7 @@
         <v>165</v>
       </c>
       <c r="P47">
-        <v>30300</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="48">
@@ -2414,46 +2414,46 @@
         <v>-</v>
       </c>
       <c r="C48">
-        <v>49.75</v>
+        <v>50</v>
       </c>
       <c r="D48">
         <v>0.25</v>
       </c>
       <c r="E48">
-        <v>0.5050505050505051</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="F48">
-        <v>49.25</v>
+        <v>49.75</v>
       </c>
       <c r="G48">
+        <v>51.25</v>
+      </c>
+      <c r="H48">
+        <v>49.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>18484688</v>
+      </c>
+      <c r="L48">
+        <v>933610.59825</v>
+      </c>
+      <c r="M48">
+        <v>332600</v>
+      </c>
+      <c r="N48">
         <v>50</v>
       </c>
-      <c r="H48">
-        <v>49.25</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>9366275</v>
-      </c>
-      <c r="L48">
-        <v>464101.732</v>
-      </c>
-      <c r="M48">
-        <v>1252000</v>
-      </c>
-      <c r="N48">
-        <v>49.5</v>
-      </c>
       <c r="O48">
-        <v>49.75</v>
+        <v>50.25</v>
       </c>
       <c r="P48">
-        <v>526900</v>
+        <v>2105600</v>
       </c>
     </row>
     <row r="49">
@@ -2464,23 +2464,23 @@
         <v>-</v>
       </c>
       <c r="C49">
+        <v>42.75</v>
+      </c>
+      <c r="D49">
+        <v>0.25</v>
+      </c>
+      <c r="E49">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="F49">
+        <v>42.75</v>
+      </c>
+      <c r="G49">
+        <v>43</v>
+      </c>
+      <c r="H49">
         <v>42.5</v>
       </c>
-      <c r="D49">
-        <v>-0.25</v>
-      </c>
-      <c r="E49">
-        <v>-0.5847953216374269</v>
-      </c>
-      <c r="F49">
-        <v>42.5</v>
-      </c>
-      <c r="G49">
-        <v>42.75</v>
-      </c>
-      <c r="H49">
-        <v>42.25</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -2488,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>2231778</v>
+        <v>1720777</v>
       </c>
       <c r="L49">
-        <v>94917.6095</v>
+        <v>73573.31375</v>
       </c>
       <c r="M49">
-        <v>242100</v>
+        <v>392400</v>
       </c>
       <c r="N49">
         <v>42.5</v>
@@ -2503,7 +2503,7 @@
         <v>42.75</v>
       </c>
       <c r="P49">
-        <v>159700</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="50">
@@ -2514,22 +2514,22 @@
         <v>-</v>
       </c>
       <c r="C50">
+        <v>12.6</v>
+      </c>
+      <c r="D50">
+        <v>-0.3</v>
+      </c>
+      <c r="E50">
+        <v>-2.3255813953488373</v>
+      </c>
+      <c r="F50">
         <v>12.9</v>
       </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
-      <c r="E50">
-        <v>0.78125</v>
-      </c>
-      <c r="F50">
-        <v>12.8</v>
-      </c>
       <c r="G50">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H50">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>3377331</v>
+        <v>2864614</v>
       </c>
       <c r="L50">
-        <v>43600.9581</v>
+        <v>36429.1913</v>
       </c>
       <c r="M50">
-        <v>334900</v>
+        <v>164700</v>
       </c>
       <c r="N50">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O50">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="P50">
-        <v>419300</v>
+        <v>204100</v>
       </c>
     </row>
     <row r="51">
@@ -2564,13 +2564,13 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-1.6129032258064515</v>
       </c>
       <c r="F51">
         <v>31</v>
@@ -2579,31 +2579,31 @@
         <v>31.25</v>
       </c>
       <c r="H51">
+        <v>30.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>2338011</v>
+      </c>
+      <c r="L51">
+        <v>71924.69825</v>
+      </c>
+      <c r="M51">
+        <v>547600</v>
+      </c>
+      <c r="N51">
+        <v>30.5</v>
+      </c>
+      <c r="O51">
         <v>30.75</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>1864108</v>
-      </c>
-      <c r="L51">
-        <v>57752.77575</v>
-      </c>
-      <c r="M51">
-        <v>385200</v>
-      </c>
-      <c r="N51">
-        <v>30.75</v>
-      </c>
-      <c r="O51">
-        <v>31</v>
-      </c>
       <c r="P51">
-        <v>96800</v>
+        <v>42900</v>
       </c>
     </row>
     <row r="52">
@@ -2614,22 +2614,22 @@
         <v>-</v>
       </c>
       <c r="C52">
+        <v>5.1</v>
+      </c>
+      <c r="D52">
+        <v>-0.5</v>
+      </c>
+      <c r="E52">
+        <v>-8.928571428571429</v>
+      </c>
+      <c r="F52">
         <v>5.6</v>
       </c>
-      <c r="D52">
-        <v>-0.1</v>
-      </c>
-      <c r="E52">
-        <v>-1.7543859649122806</v>
-      </c>
-      <c r="F52">
-        <v>5.85</v>
-      </c>
       <c r="G52">
-        <v>5.85</v>
+        <v>5.6</v>
       </c>
       <c r="H52">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>9903903</v>
+        <v>21403547</v>
       </c>
       <c r="L52">
-        <v>56251.202</v>
+        <v>113434.0209</v>
       </c>
       <c r="M52">
-        <v>643900</v>
+        <v>816700</v>
       </c>
       <c r="N52">
-        <v>5.55</v>
+        <v>5.1</v>
       </c>
       <c r="O52">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="P52">
-        <v>1186400</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="53">
@@ -2664,46 +2664,46 @@
         <v>-</v>
       </c>
       <c r="C53">
+        <v>102.5</v>
+      </c>
+      <c r="D53">
+        <v>-1</v>
+      </c>
+      <c r="E53">
+        <v>-0.966183574879227</v>
+      </c>
+      <c r="F53">
+        <v>103</v>
+      </c>
+      <c r="G53">
         <v>103.5</v>
-      </c>
-      <c r="D53">
-        <v>-0.5</v>
-      </c>
-      <c r="E53">
-        <v>-0.4807692307692308</v>
-      </c>
-      <c r="F53">
-        <v>103.5</v>
-      </c>
-      <c r="G53">
-        <v>104</v>
       </c>
       <c r="H53">
         <v>102.5</v>
       </c>
       <c r="I53">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>3146.4</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>7684973</v>
+        <v>6804620</v>
       </c>
       <c r="L53">
-        <v>791786.1195</v>
+        <v>699823.3</v>
       </c>
       <c r="M53">
-        <v>639400</v>
+        <v>1437400</v>
       </c>
       <c r="N53">
+        <v>102.5</v>
+      </c>
+      <c r="O53">
         <v>103</v>
       </c>
-      <c r="O53">
-        <v>103.5</v>
-      </c>
       <c r="P53">
-        <v>169900</v>
+        <v>467500</v>
       </c>
     </row>
     <row r="54">
@@ -2717,43 +2717,43 @@
         <v>338</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="F54">
+        <v>338</v>
+      </c>
+      <c r="G54">
+        <v>340</v>
+      </c>
+      <c r="H54">
         <v>337</v>
       </c>
-      <c r="G54">
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>2114967</v>
+      </c>
+      <c r="L54">
+        <v>716071.182</v>
+      </c>
+      <c r="M54">
+        <v>34700</v>
+      </c>
+      <c r="N54">
+        <v>338</v>
+      </c>
+      <c r="O54">
         <v>339</v>
       </c>
-      <c r="H54">
-        <v>336</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>2304687</v>
-      </c>
-      <c r="L54">
-        <v>778502.554</v>
-      </c>
-      <c r="M54">
-        <v>487000</v>
-      </c>
-      <c r="N54">
-        <v>337</v>
-      </c>
-      <c r="O54">
-        <v>338</v>
-      </c>
       <c r="P54">
-        <v>211800</v>
+        <v>286100</v>
       </c>
     </row>
     <row r="55">
@@ -2764,46 +2764,46 @@
         <v>-</v>
       </c>
       <c r="C55">
-        <v>157.5</v>
+        <v>156.5</v>
       </c>
       <c r="D55">
         <v>-1</v>
       </c>
       <c r="E55">
-        <v>-0.6309148264984227</v>
+        <v>-0.6349206349206349</v>
       </c>
       <c r="F55">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="G55">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="H55">
+        <v>156</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>372042</v>
+      </c>
+      <c r="L55">
+        <v>58281.191</v>
+      </c>
+      <c r="M55">
+        <v>6000</v>
+      </c>
+      <c r="N55">
+        <v>156.5</v>
+      </c>
+      <c r="O55">
         <v>157</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>417258</v>
-      </c>
-      <c r="L55">
-        <v>65712.735</v>
-      </c>
-      <c r="M55">
-        <v>14800</v>
-      </c>
-      <c r="N55">
-        <v>157</v>
-      </c>
-      <c r="O55">
-        <v>157.5</v>
-      </c>
       <c r="P55">
-        <v>62400</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="56">
@@ -2814,46 +2814,46 @@
         <v>-</v>
       </c>
       <c r="C56">
-        <v>53.5</v>
+        <v>52.75</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>-1.4018691588785046</v>
       </c>
       <c r="F56">
         <v>53.5</v>
       </c>
       <c r="G56">
-        <v>53.75</v>
+        <v>53.5</v>
       </c>
       <c r="H56">
-        <v>53</v>
+        <v>52.25</v>
       </c>
       <c r="I56">
-        <v>17500</v>
+        <v>615300</v>
       </c>
       <c r="J56">
-        <v>936.25</v>
+        <v>32457.075</v>
       </c>
       <c r="K56">
-        <v>5797609</v>
+        <v>10412198</v>
       </c>
       <c r="L56">
-        <v>309590.9925</v>
+        <v>549593.22075</v>
       </c>
       <c r="M56">
-        <v>199300</v>
+        <v>88800</v>
       </c>
       <c r="N56">
-        <v>53.25</v>
+        <v>52.5</v>
       </c>
       <c r="O56">
-        <v>53.5</v>
+        <v>52.75</v>
       </c>
       <c r="P56">
-        <v>145700</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="57">
@@ -2867,20 +2867,20 @@
         <v>11.4</v>
       </c>
       <c r="D57">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>2.7027027027027026</v>
+        <v>0</v>
       </c>
       <c r="F57">
+        <v>11.4</v>
+      </c>
+      <c r="G57">
+        <v>11.6</v>
+      </c>
+      <c r="H57">
         <v>11.3</v>
       </c>
-      <c r="G57">
-        <v>11.5</v>
-      </c>
-      <c r="H57">
-        <v>11.2</v>
-      </c>
       <c r="I57">
         <v>0</v>
       </c>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>30955605</v>
+        <v>13058371</v>
       </c>
       <c r="L57">
-        <v>353231.8855</v>
+        <v>149306.25530000002</v>
       </c>
       <c r="M57">
-        <v>2846200</v>
+        <v>418100</v>
       </c>
       <c r="N57">
         <v>11.3</v>
@@ -2903,7 +2903,7 @@
         <v>11.4</v>
       </c>
       <c r="P57">
-        <v>184900</v>
+        <v>683700</v>
       </c>
     </row>
     <row r="58">
@@ -2914,19 +2914,19 @@
         <v>-</v>
       </c>
       <c r="C58">
-        <v>9.95</v>
+        <v>9.9</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F58">
         <v>9.95</v>
       </c>
       <c r="G58">
-        <v>10</v>
+        <v>9.95</v>
       </c>
       <c r="H58">
         <v>9.9</v>
@@ -2938,22 +2938,22 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>1153621</v>
+        <v>928918</v>
       </c>
       <c r="L58">
-        <v>11490.54515</v>
+        <v>9227.94695</v>
       </c>
       <c r="M58">
-        <v>117100</v>
+        <v>376100</v>
       </c>
       <c r="N58">
+        <v>9.9</v>
+      </c>
+      <c r="O58">
         <v>9.95</v>
       </c>
-      <c r="O58">
-        <v>10</v>
-      </c>
       <c r="P58">
-        <v>135900</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="59">
@@ -2964,22 +2964,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="D59">
         <v>0.3</v>
       </c>
       <c r="E59">
-        <v>2.7027027027027026</v>
+        <v>2.6315789473684212</v>
       </c>
       <c r="F59">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G59">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="H59">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>26522526</v>
+        <v>37754818</v>
       </c>
       <c r="L59">
-        <v>302055.1235</v>
+        <v>442598.1054</v>
       </c>
       <c r="M59">
-        <v>1124000</v>
+        <v>1258600</v>
       </c>
       <c r="N59">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="O59">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="P59">
-        <v>556600</v>
+        <v>1145400</v>
       </c>
     </row>
     <row r="60">
@@ -3014,13 +3014,13 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>-1.5873015873015872</v>
       </c>
       <c r="F60">
         <v>0.63</v>
@@ -3038,22 +3038,22 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>42611749</v>
+        <v>43232555</v>
       </c>
       <c r="L60">
-        <v>26886.48375</v>
+        <v>27120.30886</v>
       </c>
       <c r="M60">
-        <v>9893600</v>
+        <v>34010500</v>
       </c>
       <c r="N60">
+        <v>0.62</v>
+      </c>
+      <c r="O60">
         <v>0.63</v>
       </c>
-      <c r="O60">
-        <v>0.64</v>
-      </c>
       <c r="P60">
-        <v>18546100</v>
+        <v>6283300</v>
       </c>
     </row>
     <row r="61">
@@ -3064,22 +3064,22 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>-1.092896174863388</v>
       </c>
       <c r="F61">
         <v>18.3</v>
       </c>
       <c r="G61">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="H61">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3088,22 +3088,22 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>6759324</v>
+        <v>4232498</v>
       </c>
       <c r="L61">
-        <v>123685.3796</v>
+        <v>76604.99840000001</v>
       </c>
       <c r="M61">
-        <v>96000</v>
+        <v>436000</v>
       </c>
       <c r="N61">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="O61">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P61">
-        <v>252800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="62">
@@ -3114,46 +3114,46 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F62">
         <v>16.1</v>
       </c>
       <c r="G62">
+        <v>16.6</v>
+      </c>
+      <c r="H62">
+        <v>16</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>11447811</v>
+      </c>
+      <c r="L62">
+        <v>186660.108</v>
+      </c>
+      <c r="M62">
+        <v>233300</v>
+      </c>
+      <c r="N62">
         <v>16.2</v>
       </c>
-      <c r="H62">
-        <v>15.9</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>5819119</v>
-      </c>
-      <c r="L62">
-        <v>93254.035</v>
-      </c>
-      <c r="M62">
-        <v>71300</v>
-      </c>
-      <c r="N62">
-        <v>16.1</v>
-      </c>
       <c r="O62">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P62">
-        <v>308200</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="63">
@@ -3164,37 +3164,37 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>57</v>
+        <v>57.25</v>
       </c>
       <c r="D63">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E63">
-        <v>-0.4366812227074236</v>
+        <v>0.43859649122807015</v>
       </c>
       <c r="F63">
         <v>57.5</v>
       </c>
       <c r="G63">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H63">
-        <v>56.75</v>
+        <v>57</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>775200</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>44550.37</v>
       </c>
       <c r="K63">
-        <v>9125904</v>
+        <v>12358616</v>
       </c>
       <c r="L63">
-        <v>523788.4305</v>
+        <v>712620.5205</v>
       </c>
       <c r="M63">
-        <v>10400</v>
+        <v>1227200</v>
       </c>
       <c r="N63">
         <v>57</v>
@@ -3203,7 +3203,7 @@
         <v>57.25</v>
       </c>
       <c r="P63">
-        <v>552800</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="64">
@@ -3214,46 +3214,46 @@
         <v>-</v>
       </c>
       <c r="C64">
+        <v>1.16</v>
+      </c>
+      <c r="D64">
+        <v>-0.01</v>
+      </c>
+      <c r="E64">
+        <v>-0.8547008547008547</v>
+      </c>
+      <c r="F64">
         <v>1.17</v>
       </c>
-      <c r="D64">
-        <v>0.01</v>
-      </c>
-      <c r="E64">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="F64">
+      <c r="G64">
+        <v>1.17</v>
+      </c>
+      <c r="H64">
+        <v>1.14</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>5021700</v>
+      </c>
+      <c r="L64">
+        <v>5813.152</v>
+      </c>
+      <c r="M64">
+        <v>674300</v>
+      </c>
+      <c r="N64">
+        <v>1.14</v>
+      </c>
+      <c r="O64">
         <v>1.16</v>
       </c>
-      <c r="G64">
-        <v>1.18</v>
-      </c>
-      <c r="H64">
-        <v>1.15</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>2418600</v>
-      </c>
-      <c r="L64">
-        <v>2811.27308</v>
-      </c>
-      <c r="M64">
-        <v>213000</v>
-      </c>
-      <c r="N64">
-        <v>1.16</v>
-      </c>
-      <c r="O64">
-        <v>1.17</v>
-      </c>
       <c r="P64">
-        <v>183700</v>
+        <v>54100</v>
       </c>
     </row>
     <row r="65">
@@ -3264,19 +3264,19 @@
         <v>-</v>
       </c>
       <c r="C65">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>-0.6172839506172839</v>
       </c>
       <c r="F65">
         <v>16.3</v>
       </c>
       <c r="G65">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="H65">
         <v>16.1</v>
@@ -3288,22 +3288,22 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>16289493</v>
+        <v>11030952</v>
       </c>
       <c r="L65">
-        <v>264277.7181</v>
+        <v>177788.1126</v>
       </c>
       <c r="M65">
-        <v>1328900</v>
+        <v>3467300</v>
       </c>
       <c r="N65">
+        <v>16.1</v>
+      </c>
+      <c r="O65">
         <v>16.2</v>
       </c>
-      <c r="O65">
-        <v>16.3</v>
-      </c>
       <c r="P65">
-        <v>1582700</v>
+        <v>1787400</v>
       </c>
     </row>
     <row r="66">
@@ -3314,22 +3314,22 @@
         <v>-</v>
       </c>
       <c r="C66">
+        <v>5.35</v>
+      </c>
+      <c r="D66">
+        <v>-0.2</v>
+      </c>
+      <c r="E66">
+        <v>-3.6036036036036037</v>
+      </c>
+      <c r="F66">
         <v>5.55</v>
       </c>
-      <c r="D66">
-        <v>-0.05</v>
-      </c>
-      <c r="E66">
-        <v>-0.8928571428571429</v>
-      </c>
-      <c r="F66">
-        <v>5.6</v>
-      </c>
       <c r="G66">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="H66">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3338,22 +3338,22 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>746211</v>
+        <v>1626542</v>
       </c>
       <c r="L66">
-        <v>4115.07705</v>
+        <v>8852.3157</v>
       </c>
       <c r="M66">
-        <v>700</v>
+        <v>130700</v>
       </c>
       <c r="N66">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O66">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="P66">
-        <v>79200</v>
+        <v>2300</v>
       </c>
     </row>
   </sheetData>
